--- a/MFDS 1일 섭취허용량.xlsx
+++ b/MFDS 1일 섭취허용량.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a624188ccc7a469/바탕 화면/CPCA 계산기/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a624188ccc7a469/바탕 화면/nitrosamines-AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_769BC176CB385EDFDA183B0CA155A9EDADF59F72" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF0B93A6-4A2C-4D4A-8BC2-57AF8B2FBE69}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_769BC176CB385EDFDA183B0CA155A9EDADF59F72" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45B4DB18-BB0D-4230-AD37-4B608B7537B8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="26690" yWindow="5180" windowWidth="14400" windowHeight="8240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -2529,18 +2529,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I158"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.3125" customWidth="1"/>
     <col min="3" max="3" width="32" style="1" customWidth="1"/>
     <col min="4" max="4" width="47.75" customWidth="1"/>
     <col min="5" max="5" width="23.5" customWidth="1"/>
-    <col min="8" max="8" width="27.58203125" customWidth="1"/>
+    <col min="8" max="8" width="27.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2569,7 +2568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="187" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="185.65" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -2618,7 +2617,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -2644,7 +2643,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -2667,7 +2666,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -2693,7 +2692,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -2716,7 +2715,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="289" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" ht="270" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -2742,7 +2741,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -2768,7 +2767,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -2791,7 +2790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -2840,7 +2839,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -2863,7 +2862,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -2886,7 +2885,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -2909,7 +2908,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -2932,7 +2931,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -2955,7 +2954,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>86</v>
       </c>
@@ -2978,7 +2977,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="119" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" ht="118.15" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>90</v>
       </c>
@@ -3001,7 +3000,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A20" t="s">
         <v>93</v>
       </c>
@@ -3024,7 +3023,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A21" t="s">
         <v>97</v>
       </c>
@@ -3050,7 +3049,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -3073,7 +3072,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A23" t="s">
         <v>106</v>
       </c>
@@ -3096,7 +3095,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -3119,7 +3118,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -3145,7 +3144,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A26" t="s">
         <v>124</v>
       </c>
@@ -3168,7 +3167,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A27" t="s">
         <v>128</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A28" t="s">
         <v>133</v>
       </c>
@@ -3217,7 +3216,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A29" t="s">
         <v>138</v>
       </c>
@@ -3240,7 +3239,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A30" t="s">
         <v>142</v>
       </c>
@@ -3263,7 +3262,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A31" t="s">
         <v>146</v>
       </c>
@@ -3286,7 +3285,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A32" t="s">
         <v>150</v>
       </c>
@@ -3309,7 +3308,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A33" t="s">
         <v>155</v>
       </c>
@@ -3332,7 +3331,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A34" t="s">
         <v>159</v>
       </c>
@@ -3355,7 +3354,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A35" t="s">
         <v>163</v>
       </c>
@@ -3381,7 +3380,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A36" t="s">
         <v>168</v>
       </c>
@@ -3407,7 +3406,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="102" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" ht="101.25" x14ac:dyDescent="0.6">
       <c r="A37" t="s">
         <v>175</v>
       </c>
@@ -3433,7 +3432,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A38" t="s">
         <v>181</v>
       </c>
@@ -3459,7 +3458,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A39" t="s">
         <v>186</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A40" t="s">
         <v>190</v>
       </c>
@@ -3505,7 +3504,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A41" t="s">
         <v>195</v>
       </c>
@@ -3528,7 +3527,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A42" t="s">
         <v>199</v>
       </c>
@@ -3554,7 +3553,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A43" t="s">
         <v>204</v>
       </c>
@@ -3577,7 +3576,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A44" t="s">
         <v>207</v>
       </c>
@@ -3603,7 +3602,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A45" t="s">
         <v>212</v>
       </c>
@@ -3629,7 +3628,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A46" t="s">
         <v>216</v>
       </c>
@@ -3655,7 +3654,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="102" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" ht="101.25" x14ac:dyDescent="0.6">
       <c r="A47" t="s">
         <v>221</v>
       </c>
@@ -3678,7 +3677,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A48" t="s">
         <v>225</v>
       </c>
@@ -3701,7 +3700,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A49" t="s">
         <v>229</v>
       </c>
@@ -3724,7 +3723,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A50" t="s">
         <v>233</v>
       </c>
@@ -3747,7 +3746,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A51" t="s">
         <v>237</v>
       </c>
@@ -3770,7 +3769,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A52" t="s">
         <v>242</v>
       </c>
@@ -3793,7 +3792,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A53" t="s">
         <v>246</v>
       </c>
@@ -3819,7 +3818,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A54" t="s">
         <v>250</v>
       </c>
@@ -3845,7 +3844,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="221" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" ht="202.5" x14ac:dyDescent="0.6">
       <c r="A55" t="s">
         <v>255</v>
       </c>
@@ -3868,7 +3867,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A56" t="s">
         <v>259</v>
       </c>
@@ -3894,7 +3893,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A57" t="s">
         <v>264</v>
       </c>
@@ -3920,7 +3919,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A58" t="s">
         <v>269</v>
       </c>
@@ -3946,7 +3945,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -3969,7 +3968,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A60" t="s">
         <v>276</v>
       </c>
@@ -3992,7 +3991,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A61" t="s">
         <v>280</v>
       </c>
@@ -4018,7 +4017,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A62" t="s">
         <v>285</v>
       </c>
@@ -4041,7 +4040,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -4064,7 +4063,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A64" t="s">
         <v>293</v>
       </c>
@@ -4087,7 +4086,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A65" t="s">
         <v>297</v>
       </c>
@@ -4110,7 +4109,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A66" t="s">
         <v>301</v>
       </c>
@@ -4133,7 +4132,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A67" t="s">
         <v>305</v>
       </c>
@@ -4159,7 +4158,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A68" t="s">
         <v>310</v>
       </c>
@@ -4182,7 +4181,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A69" t="s">
         <v>314</v>
       </c>
@@ -4205,7 +4204,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A70" t="s">
         <v>318</v>
       </c>
@@ -4231,7 +4230,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A71" t="s">
         <v>323</v>
       </c>
@@ -4254,7 +4253,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A72" t="s">
         <v>327</v>
       </c>
@@ -4277,7 +4276,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A73" t="s">
         <v>330</v>
       </c>
@@ -4300,7 +4299,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A74" t="s">
         <v>334</v>
       </c>
@@ -4326,7 +4325,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A75" t="s">
         <v>338</v>
       </c>
@@ -4349,7 +4348,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A76" t="s">
         <v>342</v>
       </c>
@@ -4375,7 +4374,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A77" t="s">
         <v>347</v>
       </c>
@@ -4398,7 +4397,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A78" t="s">
         <v>351</v>
       </c>
@@ -4424,7 +4423,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A79" t="s">
         <v>357</v>
       </c>
@@ -4450,7 +4449,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A80" t="s">
         <v>361</v>
       </c>
@@ -4473,7 +4472,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A81" t="s">
         <v>365</v>
       </c>
@@ -4499,7 +4498,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A82" t="s">
         <v>371</v>
       </c>
@@ -4525,7 +4524,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A83" t="s">
         <v>375</v>
       </c>
@@ -4548,7 +4547,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A84" t="s">
         <v>379</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A85" t="s">
         <v>384</v>
       </c>
@@ -4597,7 +4596,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A86" t="s">
         <v>388</v>
       </c>
@@ -4623,7 +4622,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A87" t="s">
         <v>393</v>
       </c>
@@ -4646,7 +4645,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A88" t="s">
         <v>397</v>
       </c>
@@ -4669,7 +4668,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A89" t="s">
         <v>401</v>
       </c>
@@ -4692,7 +4691,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A90" t="s">
         <v>405</v>
       </c>
@@ -4715,7 +4714,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="119" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:9" ht="118.15" x14ac:dyDescent="0.6">
       <c r="A91" t="s">
         <v>409</v>
       </c>
@@ -4738,7 +4737,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A92" t="s">
         <v>412</v>
       </c>
@@ -4764,7 +4763,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A93" t="s">
         <v>417</v>
       </c>
@@ -4790,7 +4789,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A94" t="s">
         <v>422</v>
       </c>
@@ -4816,7 +4815,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A95" t="s">
         <v>427</v>
       </c>
@@ -4839,7 +4838,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A96" t="s">
         <v>431</v>
       </c>
@@ -4865,7 +4864,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A97" t="s">
         <v>435</v>
       </c>
@@ -4888,7 +4887,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A98" t="s">
         <v>439</v>
       </c>
@@ -4914,7 +4913,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A99" t="s">
         <v>444</v>
       </c>
@@ -4937,7 +4936,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A100" t="s">
         <v>448</v>
       </c>
@@ -4960,7 +4959,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A101" t="s">
         <v>452</v>
       </c>
@@ -4983,7 +4982,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A102" t="s">
         <v>455</v>
       </c>
@@ -5009,7 +5008,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A103" t="s">
         <v>461</v>
       </c>
@@ -5032,7 +5031,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A104" t="s">
         <v>465</v>
       </c>
@@ -5055,7 +5054,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A105" t="s">
         <v>469</v>
       </c>
@@ -5078,7 +5077,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A106" t="s">
         <v>472</v>
       </c>
@@ -5101,7 +5100,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A107" t="s">
         <v>475</v>
       </c>
@@ -5124,7 +5123,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A108" t="s">
         <v>479</v>
       </c>
@@ -5147,7 +5146,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A109" t="s">
         <v>482</v>
       </c>
@@ -5173,7 +5172,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A110" t="s">
         <v>487</v>
       </c>
@@ -5196,7 +5195,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A111" t="s">
         <v>490</v>
       </c>
@@ -5222,7 +5221,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="102" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:9" ht="101.25" x14ac:dyDescent="0.6">
       <c r="A112" t="s">
         <v>495</v>
       </c>
@@ -5245,7 +5244,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A113" t="s">
         <v>499</v>
       </c>
@@ -5268,7 +5267,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A114" t="s">
         <v>503</v>
       </c>
@@ -5291,7 +5290,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A115" t="s">
         <v>507</v>
       </c>
@@ -5314,7 +5313,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A116" t="s">
         <v>511</v>
       </c>
@@ -5337,7 +5336,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A117" t="s">
         <v>515</v>
       </c>
@@ -5360,7 +5359,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A118" t="s">
         <v>519</v>
       </c>
@@ -5383,7 +5382,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A119" t="s">
         <v>523</v>
       </c>
@@ -5406,7 +5405,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A120" t="s">
         <v>526</v>
       </c>
@@ -5432,7 +5431,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A121" t="s">
         <v>530</v>
       </c>
@@ -5455,7 +5454,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A122" t="s">
         <v>533</v>
       </c>
@@ -5478,7 +5477,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A123" t="s">
         <v>536</v>
       </c>
@@ -5501,7 +5500,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A124" t="s">
         <v>540</v>
       </c>
@@ -5524,7 +5523,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A125" t="s">
         <v>543</v>
       </c>
@@ -5547,7 +5546,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A126" t="s">
         <v>547</v>
       </c>
@@ -5573,7 +5572,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A127" t="s">
         <v>552</v>
       </c>
@@ -5599,7 +5598,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A128" t="s">
         <v>557</v>
       </c>
@@ -5625,7 +5624,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A129" t="s">
         <v>562</v>
       </c>
@@ -5648,7 +5647,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A130" t="s">
         <v>566</v>
       </c>
@@ -5671,7 +5670,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A131" t="s">
         <v>570</v>
       </c>
@@ -5697,7 +5696,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A132" t="s">
         <v>575</v>
       </c>
@@ -5723,7 +5722,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A133" t="s">
         <v>580</v>
       </c>
@@ -5746,7 +5745,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A134" t="s">
         <v>584</v>
       </c>
@@ -5769,7 +5768,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:9" ht="84.4" x14ac:dyDescent="0.6">
       <c r="A135" t="s">
         <v>588</v>
       </c>
@@ -5792,7 +5791,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A136" t="s">
         <v>592</v>
       </c>
@@ -5815,7 +5814,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A137" t="s">
         <v>596</v>
       </c>
@@ -5838,7 +5837,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A138" t="s">
         <v>600</v>
       </c>
@@ -5861,7 +5860,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A139" t="s">
         <v>604</v>
       </c>
@@ -5884,7 +5883,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A140" t="s">
         <v>608</v>
       </c>
@@ -5910,7 +5909,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A141" t="s">
         <v>613</v>
       </c>
@@ -5933,7 +5932,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="85" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A142" t="s">
         <v>617</v>
       </c>
@@ -5956,7 +5955,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A143" t="s">
         <v>621</v>
       </c>
@@ -5982,7 +5981,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="51" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
       <c r="A144" t="s">
         <v>627</v>
       </c>
@@ -6008,7 +6007,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A145" t="s">
         <v>632</v>
       </c>
@@ -6034,7 +6033,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="68" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
       <c r="A146" t="s">
         <v>638</v>
       </c>
@@ -6057,7 +6056,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A147" t="s">
         <v>642</v>
       </c>
@@ -6083,7 +6082,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A148" t="s">
         <v>646</v>
       </c>
@@ -6109,7 +6108,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="34" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A149" t="s">
         <v>650</v>
       </c>
@@ -6135,7 +6134,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A150" t="s">
         <v>654</v>
       </c>
@@ -6161,7 +6160,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A151" t="s">
         <v>658</v>
       </c>
@@ -6187,7 +6186,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A152" t="s">
         <v>662</v>
       </c>
@@ -6210,7 +6209,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A153" t="s">
         <v>666</v>
       </c>
@@ -6233,7 +6232,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A154" t="s">
         <v>31</v>
       </c>
@@ -6256,7 +6255,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A155" t="s">
         <v>12</v>
       </c>
@@ -6282,7 +6281,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A156" t="s">
         <v>24</v>
       </c>
@@ -6308,7 +6307,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A157" t="s">
         <v>51</v>
       </c>
@@ -6331,7 +6330,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A158" t="s">
         <v>56</v>
       </c>
@@ -6355,13 +6354,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I158" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I158" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MFDS 1일 섭취허용량.xlsx
+++ b/MFDS 1일 섭취허용량.xlsx
@@ -117,28 +117,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N-nitroso-mefloquine</t>
+          <t>N-nitroso-carteolol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(RS)-[2,8-bis(trifluoromethyl)quinolin-4-yl]-[(2R)-1-nitrosopiperidin-2-yl]methanol</t>
+          <t>N-tert-butyl-N-[2-hydroxy-3-[(2-oxo-3,4-dihydro-1H-quinolin-5-yl)oxy]propyl]nitrous amide</t>
         </is>
       </c>
       <c r="D2"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>메플로퀸염산염(Mefloquine)</t>
+          <t>카르테올롤염산염(Carteolol Hydrochloride)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -147,42 +147,42 @@
         </is>
       </c>
       <c r="H2"/>
-      <c r="I2"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>168</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N-nitroso-hydroxyzine Impurity A</t>
+          <t>N-nitroso-mefloquine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1-((4-Chlorophenyl)(phenyl)methyl)-4-nitrosopiperazine</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2005-04-1</t>
-        </is>
-      </c>
+          <t>(RS)-[2,8-bis(trifluoromethyl)quinolin-4-yl]-[(2R)-1-nitrosopiperidin-2-yl]methanol</t>
+        </is>
+      </c>
+      <c r="D3"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>히드록시진(Hydroxyzine)</t>
+          <t>메플로퀸염산염(Mefloquine)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H3"/>
@@ -191,33 +191,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>167</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N-nitroso-hydroxychloroquine EP Impurity C</t>
+          <t>N-nitroso-hydroxyzine Impurity A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-(4-((7-Chloroquinolin-4-yl)amino)pentyl)-N-(2-hydroxyethyl)nitrous amide</t>
-        </is>
-      </c>
-      <c r="D4"/>
+          <t>1-((4-Chlorophenyl)(phenyl)methyl)-4-nitrosopiperazine</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2005-04-1</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>히드록시클로로퀸(Hydroxychloroquine)</t>
+          <t>히드록시진(Hydroxyzine)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H4"/>
@@ -226,23 +230,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>166</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N-nitroso-propafenone impurity B </t>
+          <t>N-nitroso-hydroxychloroquine EP Impurity C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(R,E)-N-(3-(2-cinnamoylphenoxy)-2-hydroxypropyl)-N-propylnitrous amide</t>
+          <t>N-(4-((7-Chloroquinolin-4-yl)amino)pentyl)-N-(2-hydroxyethyl)nitrous amide</t>
         </is>
       </c>
       <c r="D5"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>프로파페논(Propafenone)</t>
+          <t>히드록시클로로퀸(Hydroxychloroquine)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -261,23 +265,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>165</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-ulipristal acetate (NDUPA)</t>
+          <t>N-nitroso-propafenone impurity B </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[(8S,11R,13S,14S,17R)-17-acetyl-13-methyl-11-[4-[methyl(nitroso)amino]phenyl]-3-oxo-1,2,6,7,8,11,12,14,15,16-decahydrocyclopenta[a]phenanthren-17-yl] acetate</t>
+          <t>(R,E)-N-(3-(2-cinnamoylphenoxy)-2-hydroxypropyl)-N-propylnitrous amide</t>
         </is>
       </c>
       <c r="D6"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>울리프리스탈아세테이트(Ulipristal Acetate)</t>
+          <t>프로파페논(Propafenone)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -296,23 +300,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N-nitroso-venlafaxine EP Impurity H</t>
+          <t>N-nitroso-desmethyl-ulipristal acetate (NDUPA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-(2-(1-Hydroxycyclohexyl)-2-(4-methoxyphenyl)ethyl)-N-(4-methoxyphenethyl)nitrous amide</t>
+          <t>[(8S,11R,13S,14S,17R)-17-acetyl-13-methyl-11-[4-[methyl(nitroso)amino]phenyl]-3-oxo-1,2,6,7,8,11,12,14,15,16-decahydrocyclopenta[a]phenanthren-17-yl] acetate</t>
         </is>
       </c>
       <c r="D7"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>벤라팍신(Venlafaxine)</t>
+          <t>울리프리스탈아세테이트(Ulipristal Acetate)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -331,27 +335,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N-nitroso-methylethanolamine (NMELA)</t>
+          <t>N-nitroso-venlafaxine EP Impurity H</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-(2-hydroxyethyl)-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>26921-68-6</t>
-        </is>
-      </c>
+          <t>N-(2-(1-Hydroxycyclohexyl)-2-(4-methoxyphenyl)ethyl)-N-(4-methoxyphenethyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D8"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>네포팜(Nefopam)</t>
+          <t>벤라팍신(Venlafaxine)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -370,33 +370,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N-nitroso-hydroxychloroquine EP Impurity D</t>
+          <t>N-nitroso-methylethanolamine (NMELA)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-(4-((7-Chloroquinolin-4-yl)amino)pentyl)-N-ethylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D9"/>
+          <t>N-(2-hydroxyethyl)-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>26921-68-6</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>히드록시클로로퀸(Hydroxychloroquine)</t>
+          <t>네포팜(Nefopam)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H9"/>
@@ -405,23 +409,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">N-nitroso-terbinafine degradant(NTD, NHMA) </t>
+          <t>N-nitroso-hydroxychloroquine EP Impurity D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N-[(2E)-6,6-dimethyl-2-hepten-4-yn-1-yl]-N-nitrosomethanamine</t>
+          <t>N-(4-((7-Chloroquinolin-4-yl)amino)pentyl)-N-ethylnitrous amide</t>
         </is>
       </c>
       <c r="D10"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>테르비나핀(Terbinafine)</t>
+          <t>히드록시클로로퀸(Hydroxychloroquine)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -440,23 +444,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-almotriptan</t>
+          <t xml:space="preserve">N-nitroso-terbinafine degradant(NTD, NHMA) </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>N-methyl-N-[2-[5-(pyrrolidin-1-ylsulfonylmethyl)-1H-indol-3-yl]ethyl]nitrous amide</t>
+          <t>N-[(2E)-6,6-dimethyl-2-hepten-4-yn-1-yl]-N-nitrosomethanamine</t>
         </is>
       </c>
       <c r="D11"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>알모트립탄(Almotriptan)</t>
+          <t>테르비나핀(Terbinafine)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -475,27 +479,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>N-nitroso-venlafaxine EP Impurity D</t>
+          <t>N-nitroso-desmethyl-almotriptan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>N-(2-benzoyl-4-chlorophenyl)-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>51145-18-7</t>
-        </is>
-      </c>
+          <t>N-methyl-N-[2-[5-(pyrrolidin-1-ylsulfonylmethyl)-1H-indol-3-yl]ethyl]nitrous amide</t>
+        </is>
+      </c>
+      <c r="D12"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>벤라팍신(Venlafaxine)</t>
+          <t>알모트립탄(Almotriptan)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -514,158 +514,158 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl roxithromycin</t>
+          <t>N-nitroso-venlafaxine EP Impurity D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>N-((2S,3R,4S,6R)-2-(((3R,4S,5S,6R,7R,9R,11S,12R,13S,14R,E)-14-ethyl-7,12,13-trihydroxy-4-(((2R,4R,5S,6S)-5-hydroxy-4-methoxy-4,6-dimethyltetrahydro-2H-pyran-2-yl)oxy)-10-(((2-methoxyethoxy)methoxy)imino)-3,5,7,9,11,13-hexamethyl-2-oxooxacyclotetradecan-6-yl)oxy)-3-hydroxy-6-methyltetrahydro-2H-pyran-4-yl)-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D13"/>
+          <t>N-(2-benzoyl-4-chlorophenyl)-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>51145-18-7</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>록시트로마이신(Roxithromycin)</t>
+          <t>벤라팍신(Venlafaxine)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H13"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+      <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>N-nitroso-vonoprazan</t>
+          <t>N-nitroso-N-desmethyl roxithromycin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>N-[[5-(2-fluorophenyl)-1-pyridin-3-ylsulfonylpyrrol-3-yl]methyl]-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2932441-73-9</t>
-        </is>
-      </c>
+          <t>N-((2S,3R,4S,6R)-2-(((3R,4S,5S,6R,7R,9R,11S,12R,13S,14R,E)-14-ethyl-7,12,13-trihydroxy-4-(((2R,4R,5S,6S)-5-hydroxy-4-methoxy-4,6-dimethyltetrahydro-2H-pyran-2-yl)oxy)-10-(((2-methoxyethoxy)methoxy)imino)-3,5,7,9,11,13-hexamethyl-2-oxooxacyclotetradecan-6-yl)oxy)-3-hydroxy-6-methyltetrahydro-2H-pyran-4-yl)-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D14"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>보노프라잔(Vonoprazan)</t>
-        </is>
-      </c>
-      <c r="F14"/>
+          <t>록시트로마이신(Roxithromycin)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>SAR/read-across, 참조물질 NDMA</t>
-        </is>
-      </c>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H14"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N-nitroso-carvedilol</t>
+          <t>N-nitroso-vonoprazan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>N-(3-((9H-Carbazol-4-yl)oxy)-2-hydroxypropyl)-N-(2-(2-methoxyphenoxy)ethyl)nitrous amide</t>
+          <t>N-[[5-(2-fluorophenyl)-1-pyridin-3-ylsulfonylpyrrol-3-yl]methyl]-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2248746-67-8</t>
+          <t>2932441-73-9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>카르베딜롤(Carvedilol)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>보노프라잔(Vonoprazan)</t>
+        </is>
+      </c>
+      <c r="F15"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H15"/>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SAR/read-across, 참조물질 NDMA</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N-nitroso-olanzapine</t>
+          <t>N-nitroso-carvedilol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2-methyl-4-(4-methylpiperazin-1-yl)-10-nitrosothieno[2,3-b][1,5]benzodiazepine</t>
-        </is>
-      </c>
-      <c r="D16"/>
+          <t>N-(3-((9H-Carbazol-4-yl)oxy)-2-hydroxypropyl)-N-(2-(2-methoxyphenoxy)ethyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2248746-67-8</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>올란자핀(Olanzapine)</t>
+          <t>카르베딜롤(Carvedilol)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H16"/>
@@ -678,32 +678,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>N-nitroso-ephedrine</t>
+          <t>N-nitroso-olanzapine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>N-[(1S,2R)-1-hydroxy-1-phenylpropan-2-yl]-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>7181-48-8</t>
-        </is>
-      </c>
+          <t>2-methyl-4-(4-methylpiperazin-1-yl)-10-nitrosothieno[2,3-b][1,5]benzodiazepine</t>
+        </is>
+      </c>
+      <c r="D17"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>에페드린(Ephedrine)</t>
+          <t>올란자핀(Olanzapine)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -721,28 +717,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>N-nitroso-evocalcet</t>
+          <t>N-nitroso-ephedrine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2-(4-((S)-3-(((R)-1-(naphthalen-1-yl)ethyl)(nitroso)amino)pyrrolidin-1-yl)phenyl)acetic acid</t>
-        </is>
-      </c>
-      <c r="D18"/>
+          <t>N-[(1S,2R)-1-hydroxy-1-phenylpropan-2-yl]-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7181-48-8</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>에보칼세트(Evocalcet)</t>
+          <t>에페드린(Ephedrine)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -760,32 +760,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N-nitroso-vancomycin</t>
+          <t>N-nitroso-evocalcet</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(1S,2R,18R,19R,22S,25R,28R,40S)-48-[(2S,3R,4S,5S,6R)-3-[(2S,4S,5S,6S)-4-amino-5-hydroxy-4,6-dimethyloxan-2-yl]oxy-4,5-dihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-22-(2-amino-2-oxoethyl)-5,15-dichloro-2,18,32,35,37-pentahydroxy-19-[[(2R)-4-methyl-2-[methyl(nitroso)amino]pentanoyl]amino]-20,23,26,42,44-pentaoxo-7,13-dioxa-21,24,27,41,43-pentazaoctacyclo[26.14.2.23,6.214,17.18,12.129,33.010,25.034,39]pentaconta-3,5,8(48),9,11,14,16,29(45),30,32,34(39),35,37,46,49-pentadecaene-40-carboxylic acid</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>155386-25-7</t>
-        </is>
-      </c>
+          <t>2-(4-((S)-3-(((R)-1-(naphthalen-1-yl)ethyl)(nitroso)amino)pyrrolidin-1-yl)phenyl)acetic acid</t>
+        </is>
+      </c>
+      <c r="D19"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>반코마이신(Vancomycin)</t>
+          <t>에보칼세트(Evocalcet)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -803,37 +799,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N-nitroso-meglumine</t>
+          <t>N-nitroso-vancomycin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>N-methyl-N-(2,3,4,5,6-pentahydroxyhexyl)nitrous amide</t>
+          <t>(1S,2R,18R,19R,22S,25R,28R,40S)-48-[(2S,3R,4S,5S,6R)-3-[(2S,4S,5S,6S)-4-amino-5-hydroxy-4,6-dimethyloxan-2-yl]oxy-4,5-dihydroxy-6-(hydroxymethyl)oxan-2-yl]oxy-22-(2-amino-2-oxoethyl)-5,15-dichloro-2,18,32,35,37-pentahydroxy-19-[[(2R)-4-methyl-2-[methyl(nitroso)amino]pentanoyl]amino]-20,23,26,42,44-pentaoxo-7,13-dioxa-21,24,27,41,43-pentazaoctacyclo[26.14.2.23,6.214,17.18,12.129,33.010,25.034,39]pentaconta-3,5,8(48),9,11,14,16,29(45),30,32,34(39),35,37,46,49-pentadecaene-40-carboxylic acid</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>62137-31-9</t>
+          <t>155386-25-7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>메글루민(Meglumine)</t>
+          <t>반코마이신(Vancomycin)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H20"/>
@@ -846,33 +842,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>N-nitroso-despropyl-ropinirole</t>
+          <t>N-nitroso-meglumine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>N-(2-(2-oxoindolin-4-yl)ethyl)-N-propylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D21"/>
+          <t>N-methyl-N-(2,3,4,5,6-pentahydroxyhexyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>62137-31-9</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>로피니롤(Ropinirole)</t>
+          <t>메글루민(Meglumine)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H21"/>
@@ -885,37 +885,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>149</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>N-nitroso-4-phenylpiperazine </t>
+          <t>N-nitroso-despropyl-ropinirole</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1-nitroso-4-phenylpiperazine</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>14340-33-1</t>
-        </is>
-      </c>
+          <t>N-(2-(2-oxoindolin-4-yl)ethyl)-N-propylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D22"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>레보드로프로피진(Levodropropizine)</t>
+          <t>로피니롤(Ropinirole)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H22"/>
@@ -928,33 +924,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-lercanidipine impurity C (EP)</t>
+          <t>N-nitroso-4-phenylpiperazine </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-(1-((3,3-diphenylpropyl)(nitroso)amino)-2-methylpropan-2-yl) 5-methyl 2,6-dimethyl-4-(3-nitrophenyl) pyridine-3,5-dicarboxylate </t>
-        </is>
-      </c>
-      <c r="D23"/>
+          <t>1-nitroso-4-phenylpiperazine</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>14340-33-1</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>레르카니디핀(Lercanidipine)</t>
+          <t>레보드로프로피진(Levodropropizine)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H23"/>
@@ -967,17 +967,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-lercanidipine</t>
+          <t>N-nitroso-desmethyl-lercanidipine impurity C (EP)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3-(1-((3,3-diphenylpropyl)(nitroso)amino)-2-methylpropan-2-yl) 5-methyl 2,6-dimethyl-4-(3-nitrophenyl) -1,4-dihydropyridine-3,5-dicarboxylate</t>
+          <t xml:space="preserve">3-(1-((3,3-diphenylpropyl)(nitroso)amino)-2-methylpropan-2-yl) 5-methyl 2,6-dimethyl-4-(3-nitrophenyl) pyridine-3,5-dicarboxylate </t>
         </is>
       </c>
       <c r="D24"/>
@@ -1006,111 +1006,111 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>N-nitroso-doravirine dimer</t>
+          <t>N-nitroso-desmethyl-lercanidipine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>N,N-bis[[3-[[3-(3-chloro-5-cyanophenoxy)-2-oxo-4-(trifluoromethyl)-1-pyridinyl]methyl]-4-methyl-5-oxo-1,2,4-triazol-1-yl]methyl]nitrous amide</t>
+          <t>3-(1-((3,3-diphenylpropyl)(nitroso)amino)-2-methylpropan-2-yl) 5-methyl 2,6-dimethyl-4-(3-nitrophenyl) -1,4-dihydropyridine-3,5-dicarboxylate</t>
         </is>
       </c>
       <c r="D25"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>도라비린(Doravirine)</t>
-        </is>
-      </c>
-      <c r="F25"/>
+          <t>레르카니디핀(Lercanidipine)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>AMES 음성</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H25"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">N-nitroso-posaconazole Impurity 1 </t>
+          <t>N-nitroso-doravirine dimer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1-(4-(((3R,5R)-5-((1H-1,2,4-triazol-1-yl)methyl)-5-(2,4-difluorophenyl)tetrahydrofuran-3-yl)methoxy)phenyl)-4-nitrosopiperazine</t>
+          <t>N,N-bis[[3-[[3-(3-chloro-5-cyanophenoxy)-2-oxo-4-(trifluoromethyl)-1-pyridinyl]methyl]-4-methyl-5-oxo-1,2,4-triazol-1-yl]methyl]nitrous amide</t>
         </is>
       </c>
       <c r="D26"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>포사코나졸(Posaconazole)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>도라비린(Doravirine)</t>
+        </is>
+      </c>
+      <c r="F26"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H26"/>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>AMES 음성</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-01-02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>N-nitroso-trientine Impurity 1</t>
+          <t xml:space="preserve">N-nitroso-posaconazole Impurity 1 </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>N-(2-aminoethyl)-N-(2-((2-aminoethyl)amino)ethyl)nitrous amide</t>
+          <t>1-(4-(((3R,5R)-5-((1H-1,2,4-triazol-1-yl)methyl)-5-(2,4-difluorophenyl)tetrahydrofuran-3-yl)methoxy)phenyl)-4-nitrosopiperazine</t>
         </is>
       </c>
       <c r="D27"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>트리엔틴(Trientine)</t>
+          <t>포사코나졸(Posaconazole)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H27"/>
@@ -1123,23 +1123,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-zolmitriptan</t>
+          <t>N-nitroso-trientine Impurity 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>N-methyl-N-[2-[5-[[(4S)-2-oxo-1,3-oxazolidin-4-yl]methyl]-1H-indol-3-yl]ethyl]nitrous amide</t>
+          <t>N-(2-aminoethyl)-N-(2-((2-aminoethyl)amino)ethyl)nitrous amide</t>
         </is>
       </c>
       <c r="D28"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>졸미트립탄(Zolmitriptan)</t>
+          <t>트리엔틴(Trientine)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1162,33 +1162,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N-nitroso-articaine</t>
+          <t>N-nitroso-desmethyl-zolmitriptan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Methyl 4-methyl-3-(2-(nitroso(propyl)amino)propanamido)thiophene-2-carboxylate</t>
+          <t>N-methyl-N-[2-[5-[[(4S)-2-oxo-1,3-oxazolidin-4-yl]methyl]-1H-indol-3-yl]ethyl]nitrous amide</t>
         </is>
       </c>
       <c r="D29"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>아티카인(Articaine)</t>
+          <t>졸미트립탄(Zolmitriptan)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H29"/>
@@ -1201,28 +1201,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>N-nitroso-acarbose</t>
+          <t>N-nitroso-articaine</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>N-nitroso-4,6-dideoxy-4-[(1S,2S,3R,4S,5S)-3,4,5-trihydroxy-2-(hydroxymethyl)cyclohexyl]-α-D-glucopyranosyl-(1→4)-α-D-glucopyranosyl-(1→4)-α-D-glucopyranosyl-(1→4)-D-glucopyranose</t>
+          <t>Methyl 4-methyl-3-(2-(nitroso(propyl)amino)propanamido)thiophene-2-carboxylate</t>
         </is>
       </c>
       <c r="D30"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>아카보즈(Acarbose)</t>
+          <t>아티카인(Articaine)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1240,28 +1240,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>N-nitroso-argatroban</t>
+          <t>N-nitroso-acarbose</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(2R,4R)-4-methyl-1-(((3-methyl-1-nitroso-1,2,3,4-tetrahydroquinolin-8-yl)sulfonyl)-L-arginyl)piperidine-2-carboxylic acid</t>
+          <t>N-nitroso-4,6-dideoxy-4-[(1S,2S,3R,4S,5S)-3,4,5-trihydroxy-2-(hydroxymethyl)cyclohexyl]-α-D-glucopyranosyl-(1→4)-α-D-glucopyranosyl-(1→4)-α-D-glucopyranosyl-(1→4)-D-glucopyranose</t>
         </is>
       </c>
       <c r="D31"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>아가트로반(Argatroban)</t>
+          <t>아카보즈(Acarbose)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1279,37 +1279,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>N-nitroso-piperazine (NPZ)</t>
+          <t>N-nitroso-argatroban</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1-nitrosopiperazine</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>5632-47-3</t>
-        </is>
-      </c>
+          <t>(2R,4R)-4-methyl-1-(((3-methyl-1-nitroso-1,2,3,4-tetrahydroquinolin-8-yl)sulfonyl)-L-arginyl)piperidine-2-carboxylic acid</t>
+        </is>
+      </c>
+      <c r="D32"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>시프로플록사신(Ciprofloxacin)</t>
+          <t>아가트로반(Argatroban)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H32"/>
@@ -1322,33 +1318,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>N-nitroso-vibegron</t>
+          <t>N-nitroso-piperazine (NPZ)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(S)-N-(4-(((2R,5S)-5-((R)-hydroxy(phenyl)methyl)-1-nitrosopyrrolidin-2-yl)methyl)phenyl)-4-oxo-4,6,7,8-tetrahydropyrrolo[1,2-a]pyrimidine-6-carboxamide</t>
-        </is>
-      </c>
-      <c r="D33"/>
+          <t>1-nitrosopiperazine</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5632-47-3</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>비베그론(Vibegron)</t>
+          <t>시프로플록사신(Ciprofloxacin)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H33"/>
@@ -1361,33 +1361,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4-(methylnitrosoamino)-1-(3-pyridinyl)-1-butanone (NNK)</t>
+          <t>N-nitroso-vibegron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>N-methyl-N-(4-oxo-4-pyridin-3-ylbutyl)nitrous amide</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>64091-91-4</t>
-        </is>
-      </c>
+          <t>(S)-N-(4-(((2R,5S)-5-((R)-hydroxy(phenyl)methyl)-1-nitrosopyrrolidin-2-yl)methyl)phenyl)-4-oxo-4,6,7,8-tetrahydropyrrolo[1,2-a]pyrimidine-6-carboxamide</t>
+        </is>
+      </c>
+      <c r="D34"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F34"/>
+          <t>비베그론(Vibegron)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H34"/>
@@ -1400,77 +1400,73 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>N-nitroso-hydrochlorothiazide</t>
+          <t>4-(methylnitrosoamino)-1-(3-pyridinyl)-1-butanone (NNK)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6-chloro-4-nitroso-1,1-dioxo-2,3-dihydro-1λ6,2,4-benzothiadiazine-7-sulfonamide</t>
-        </is>
-      </c>
-      <c r="D35"/>
+          <t>N-methyl-N-(4-oxo-4-pyridin-3-ylbutyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>64091-91-4</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>히드로클로로티아지드(Hydrochlorothiazide)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F35"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ICH Q3A/Q3B에 따라 관리</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>비변이원성 불순물, in vivo</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H35"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-08-20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>N-nitroso-fluoxetine</t>
+          <t>N-nitroso-hydrochlorothiazide</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>N-methyl-N-[3-phenyl-3-[4-(trifluoromethyl)phenoxy]propyl]nitrous amide</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>150494-06-7</t>
-        </is>
-      </c>
+          <t>6-chloro-4-nitroso-1,1-dioxo-2,3-dihydro-1λ6,2,4-benzothiadiazine-7-sulfonamide</t>
+        </is>
+      </c>
+      <c r="D36"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>플루옥세틴(Fluoxetine)</t>
+          <t>히드로클로로티아지드(Hydrochlorothiazide)</t>
         </is>
       </c>
       <c r="F36"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>ICH Q3A/Q3B에 따라 관리</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SAR/read-across, 참조물질 NNK</t>
+          <t>비변이원성 불순물, in vivo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1482,36 +1478,40 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>N-nitroso-flecainide</t>
+          <t>N-nitroso-fluoxetine</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>N-((1-Nitrosopiperidin-2-yl)methyl)-2, 5-bis(2, 2, 2-trifluoroethoxy)benzamide</t>
-        </is>
-      </c>
-      <c r="D37"/>
+          <t>N-methyl-N-[3-phenyl-3-[4-(trifluoromethyl)phenoxy]propyl]nitrous amide</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>150494-06-7</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>플레카이니드(Flecainide)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>플루옥세틴(Fluoxetine)</t>
+        </is>
+      </c>
+      <c r="F37"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H37"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SAR/read-across, 참조물질 NNK</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>2023-12-13</t>
@@ -1521,27 +1521,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>N-nitroso-propranolol</t>
+          <t>N-nitroso-flecainide</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>N-(2-hydroxy-3-naphthalen-1-yloxypropyl)-N-propan-2-ylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>84418-35-9</t>
-        </is>
-      </c>
+          <t>N-((1-Nitrosopiperidin-2-yl)methyl)-2, 5-bis(2, 2, 2-trifluoroethoxy)benzamide</t>
+        </is>
+      </c>
+      <c r="D38"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>프로프라놀롤(Propranolol)</t>
+          <t>플레카이니드(Flecainide)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1564,101 +1560,105 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>N-nitroso-propafenone</t>
+          <t>N-nitroso-propranolol</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>N-(2-hydroxy-3-(2-(3-phenylpropanoyl)phenoxy)propyl)-N-propylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D39"/>
+          <t>N-(2-hydroxy-3-naphthalen-1-yloxypropyl)-N-propan-2-ylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>84418-35-9</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>프로파페논(Propafenone)</t>
+          <t>프로프라놀롤(Propranolol)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H39"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N-nitroso-frovatriptan</t>
+          <t>N-nitroso-propafenone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(6R)-6-[methyl(nitroso)amino]-6,7,8,9-tetrahydro-5H-carbazole-3-carboxamide</t>
+          <t>N-(2-hydroxy-3-(2-(3-phenylpropanoyl)phenoxy)propyl)-N-propylnitrous amide</t>
         </is>
       </c>
       <c r="D40"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>프로바트립탄(Frovatriptan)</t>
+          <t>프로파페논(Propafenone)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H40"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N-nitroso-pramipexole</t>
+          <t>N-nitroso-frovatriptan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>N-(2-amino-4, 5, 6, 7-tetrahydrobenzo[d]thiazol-6-yl)-N-propylnitrous amide</t>
+          <t>(6R)-6-[methyl(nitroso)amino]-6,7,8,9-tetrahydro-5H-carbazole-3-carboxamide</t>
         </is>
       </c>
       <c r="D41"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>프라미펙솔(Pramipexole)</t>
+          <t>프로바트립탄(Frovatriptan)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1681,33 +1681,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>N-nitroso-furosemide</t>
+          <t>N-nitroso-pramipexole</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4-chloro-2-[furan-2-ylmethyl(nitroso)amino]-5-sulfamoylbenzoic acid</t>
+          <t>N-(2-amino-4, 5, 6, 7-tetrahydrobenzo[d]thiazol-6-yl)-N-propylnitrous amide</t>
         </is>
       </c>
       <c r="D42"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>푸로세미드(Furosemide)</t>
+          <t>프라미펙솔(Pramipexole)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H42"/>
@@ -1720,101 +1720,101 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N-nitroso-calcium folinate</t>
+          <t>N-nitroso-furosemide</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>N-[4-[[(2-amino-5-formyl-1,4,5,6,7,8-hexahydro-4-oxo-6-pteridinyl)methyl](nitroso)amino]benzoyl]-L-glutamic acid</t>
+          <t>4-chloro-2-[furan-2-ylmethyl(nitroso)amino]-5-sulfamoylbenzoic acid</t>
         </is>
       </c>
       <c r="D43"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>폴리네이트칼슘(Calcium folinate/ Calcium levofolinate)</t>
-        </is>
-      </c>
-      <c r="F43"/>
+          <t>푸로세미드(Furosemide)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ICH Q3A/Q3B에 따라 관리</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>비변이원성 불순물, in vivo</t>
-        </is>
-      </c>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H43"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>N-nitroso-felodipine</t>
+          <t>N-nitroso-calcium folinate</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 5-O-ethyl 3-O-methyl 4-(2,3-dichlorophenyl)-2,6-dimethyl-1-nitroso-4H-pyridine-3,5-dicarboxylate</t>
+          <t>N-[4-[[(2-amino-5-formyl-1,4,5,6,7,8-hexahydro-4-oxo-6-pteridinyl)methyl](nitroso)amino]benzoyl]-L-glutamic acid</t>
         </is>
       </c>
       <c r="D44"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>펠로디핀(Felodipine)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>폴리네이트칼슘(Calcium folinate/ Calcium levofolinate)</t>
+        </is>
+      </c>
+      <c r="F44"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H44"/>
+          <t>ICH Q3A/Q3B에 따라 관리</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>비변이원성 불순물, in vivo</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>N-nitroso-perindopril</t>
+          <t>N-nitroso-felodipine</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(2S,3aS,7aS)-1-[(2S)-2-[[(2S)-1-ethoxy-1-oxopentan-2-yl]-nitrosoamino]propanoyl]-2,3,3a,4,5,6,7,7a-octahydroindole-2-carboxylic acid</t>
+          <t xml:space="preserve"> 5-O-ethyl 3-O-methyl 4-(2,3-dichlorophenyl)-2,6-dimethyl-1-nitroso-4H-pyridine-3,5-dicarboxylate</t>
         </is>
       </c>
       <c r="D45"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>페린도프릴(Perindopril)</t>
+          <t>펠로디핀(Felodipine)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1837,37 +1837,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>N-nitroso-phenylephrine</t>
+          <t>N-nitroso-perindopril</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>N-[(2R)-2-hydroxy-2-(3-hydroxyphenyl)ethyl]-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>78658-64-7</t>
-        </is>
-      </c>
+          <t>(2S,3aS,7aS)-1-[(2S)-2-[[(2S)-1-ethoxy-1-oxopentan-2-yl]-nitrosoamino]propanoyl]-2,3,3a,4,5,6,7,7a-octahydroindole-2-carboxylic acid</t>
+        </is>
+      </c>
+      <c r="D46"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>페닐레프린(Phenylephrine)</t>
+          <t>페린도프릴(Perindopril)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H46"/>
@@ -1880,40 +1876,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>N-nitroso-paroxetine</t>
+          <t>N-nitroso-phenylephrine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>(3S,4R)-3-(1,3-benzodioxol-5-yloxymethyl)-4-(4-fluorophenyl)-1-nitrosopiperidine</t>
+          <t>N-[(2R)-2-hydroxy-2-(3-hydroxyphenyl)ethyl]-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2361294-43-9</t>
+          <t>78658-64-7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>파록세틴(Paroxetine)</t>
-        </is>
-      </c>
-      <c r="F47"/>
+          <t>페닐레프린(Phenylephrine)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>SAR/read-across, 참조물질 NPIP</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H47"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2023-12-13</t>
@@ -1923,119 +1919,123 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>N-nitroso-ticagrelor</t>
+          <t>N-nitroso-paroxetine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>N-((1R, 2S)-2-(3, 4-difluorophenyl)cyclopropyl)-N-(3-((1R, 2S, 3S, 4S)-2, 3-dihydroxy-4-(2-hydroxyethoxy)cyclopentyl)-5-(propylthio)-3H-[1, 2, 3]triazolo[4, 5-d]pyrimidin-7-yl)nitrous amide</t>
+          <t>(3S,4R)-3-(1,3-benzodioxol-5-yloxymethyl)-4-(4-fluorophenyl)-1-nitrosopiperidine</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2476859-55-7</t>
+          <t>2361294-43-9</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>티카그렐러(Ticagrelor)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>파록세틴(Paroxetine)</t>
+        </is>
+      </c>
+      <c r="F48"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H48"/>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SAR/read-across, 참조물질 NPIP</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>N-nitroso-trimetazidine (NTMZ)</t>
+          <t>N-nitroso-ticagrelor</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1-nitroso-4-[(2,3,4-trimethoxyphenyl)methyl]piperazine</t>
+          <t>N-((1R, 2S)-2-(3, 4-difluorophenyl)cyclopropyl)-N-(3-((1R, 2S, 3S, 4S)-2, 3-dihydroxy-4-(2-hydroxyethoxy)cyclopentyl)-5-(propylthio)-3H-[1, 2, 3]triazolo[4, 5-d]pyrimidin-7-yl)nitrous amide</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>92432-50-3</t>
+          <t>2476859-55-7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>트리메타지딘(Trimetazidine)</t>
+          <t>티카그렐러(Ticagrelor)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H49"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-01-18</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-trimebutine</t>
+          <t>N-nitroso-trimetazidine (NTMZ)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2-(Methyl(nitroso)amino)-2-phenylbutyl 3, 4, 5-trimethoxybenzoate</t>
-        </is>
-      </c>
-      <c r="D50"/>
+          <t>1-nitroso-4-[(2,3,4-trimethoxyphenyl)methyl]piperazine</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>92432-50-3</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>트리메부틴(Trimebutine)</t>
+          <t>트리메타지딘(Trimetazidine)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H50"/>
@@ -2048,141 +2048,141 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-tramadol</t>
+          <t>N-nitroso-N-desmethyl-trimebutine</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>N-[[(1R,2R)-2-hydroxy-2-(3-methoxyphenyl)cyclohexyl]methyl]-N-methylnitrous amide</t>
+          <t>2-(Methyl(nitroso)amino)-2-phenylbutyl 3, 4, 5-trimethoxybenzoate</t>
         </is>
       </c>
       <c r="D51"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>트라마돌(Tramadol)</t>
+          <t>트리메부틴(Trimebutine)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H51"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>N-nitroso-tetracaine</t>
+          <t>N-nitroso-N-desmethyl-tramadol</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2-(dimethylamino)ethyl 4-(butyl(nitroso)amino)benzoate</t>
+          <t>N-[[(1R,2R)-2-hydroxy-2-(3-methoxyphenyl)cyclohexyl]methyl]-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D52"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>테트라카인(Tetracaine)</t>
+          <t>트라마돌(Tramadol)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H52"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">N-nitroso-terbinafine impurity A </t>
+          <t>N-nitroso-tetracaine</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>N-methyl-N-(napthalen-1-ylmethyl)nitrous amide</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>296760-88-8</t>
-        </is>
-      </c>
+          <t>2-(dimethylamino)ethyl 4-(butyl(nitroso)amino)benzoate</t>
+        </is>
+      </c>
+      <c r="D53"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>테르비나핀(Terbinafine)</t>
+          <t>테트라카인(Tetracaine)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H53"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-01-18</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-terbinafine</t>
+          <t xml:space="preserve">N-nitroso-terbinafine impurity A </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>(E)-N-(6,6-Dimethylhept-2-en-4-yn-1-yl)-N-(naphthalen-1-ylmethyl)nitrous amide</t>
-        </is>
-      </c>
-      <c r="D54"/>
+          <t>N-methyl-N-(napthalen-1-ylmethyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>296760-88-8</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>테르비나핀(Terbinafine)</t>
@@ -2208,63 +2208,63 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>N-nitroso terazosin impurity N</t>
+          <t>N-nitroso-N-desmethyl-terbinafine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(4-Nitrosopiperazin-1-yl) (tetrahydrofuran-2-yl)methanone</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2470438-57-2</t>
-        </is>
-      </c>
+          <t>(E)-N-(6,6-Dimethylhept-2-en-4-yn-1-yl)-N-(naphthalen-1-ylmethyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D55"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>테라조신(Terazosin)</t>
+          <t>테르비나핀(Terbinafine)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H55"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>N-nitroso terazosin impurity C</t>
+          <t>N-nitroso terazosin impurity N</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>6,7-dimethoxy-2-(4-nitrosopiperazin-1-yl)quinazolin-4-amine</t>
-        </is>
-      </c>
-      <c r="D56"/>
+          <t>(4-Nitrosopiperazin-1-yl) (tetrahydrofuran-2-yl)methanone</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2470438-57-2</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>테라조신(Terazosin)</t>
@@ -2290,71 +2290,71 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>N-nitroso-tamsulosin</t>
+          <t>N-nitroso terazosin impurity C</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5-[(2R)-2-[2-(2-ethoxyphenoxy)ethyl-nitrosoamino]propyl]-2-methoxybenzenesulfonamide</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2892260-31-8</t>
-        </is>
-      </c>
+          <t>6,7-dimethoxy-2-(4-nitrosopiperazin-1-yl)quinazolin-4-amine</t>
+        </is>
+      </c>
+      <c r="D57"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>탐스로신(Tamsulosin)</t>
+          <t>테라조신(Terazosin)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H57"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>N-nitroso-tigecycline</t>
+          <t>N-nitroso-tamsulosin</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(4S, 4aS, 5aR, 12aS)-9-(2-(tert-butyl(nitroso)amino)acetamido)-4, 7-bis(dimethylamino)-3, 10, 12, 12a-tetrahydroxy-1, 11-dioxo-1, 4, 4a, 5, 5a, 6, 11, 12a-octahydrotetracene-2-carboxamide</t>
-        </is>
-      </c>
-      <c r="D58"/>
+          <t>5-[(2R)-2-[2-(2-ethoxyphenoxy)ethyl-nitrosoamino]propyl]-2-methoxybenzenesulfonamide</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2892260-31-8</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>타이가사이클린(Tigecycline)</t>
+          <t>탐스로신(Tamsulosin)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2372,309 +2372,309 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-tamoxifen</t>
+          <t>N-nitroso-tigecycline</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>(Z)-N-(2-(4-(1, 2-diphenylbut-1-en-1-yl)phenoxy)ethyl)-N-methylnitrous amide</t>
+          <t>(4S, 4aS, 5aR, 12aS)-9-(2-(tert-butyl(nitroso)amino)acetamido)-4, 7-bis(dimethylamino)-3, 10, 12, 12a-tetrahydroxy-1, 11-dioxo-1, 4, 4a, 5, 5a, 6, 11, 12a-octahydrotetracene-2-carboxamide</t>
         </is>
       </c>
       <c r="D59"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>타목시펜(Tamoxifen)</t>
+          <t>타이가사이클린(Tigecycline)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H59"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>N-nitroso-clozapine</t>
+          <t>N-nitroso-desmethyl-tamoxifen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8-chloro-11-(4-methylpiperazin-1-yl)-5-nitroso-5H-dibenzo[b,e][1,4]diazepine</t>
+          <t>(Z)-N-(2-(4-(1, 2-diphenylbut-1-en-1-yl)phenoxy)ethyl)-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D60"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>클로자핀(Cloazapine)</t>
+          <t>타목시펜(Tamoxifen)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H60"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>N-nitroso-clozapine EP Impurity C</t>
+          <t>N-nitroso-clozapine</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>8-chloro-11-(4-nitrosopiperazin-1-yl)-5H-dibenzo[b, e][1, 4]diazepine</t>
+          <t>8-chloro-11-(4-methylpiperazin-1-yl)-5-nitroso-5H-dibenzo[b,e][1,4]diazepine</t>
         </is>
       </c>
       <c r="D61"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>클로자핀(Clozapine)</t>
+          <t>클로자핀(Cloazapine)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H61"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl clarithromycin</t>
+          <t>N-nitroso-clozapine EP Impurity C</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>N-[(2S,3R,4S,6R)-2-[[(3R,4S,5S,6R,7R,9R,11R,12R,13S,14R)-14-ethyl-12,13-dihydroxy-4-[(2R,4R,5S,6S)-5-hydroxy-4-methoxy-4,6-dimethyloxan-2-yl]oxy-7-methoxy-3,5,7,9,11,13-hexamethyl-2,10-dioxo-oxacyclotetradec-6-yl]oxy]-3-hydroxy-6-methyloxan-4-yl]-N-methylnitrous amide</t>
+          <t>8-chloro-11-(4-nitrosopiperazin-1-yl)-5H-dibenzo[b, e][1, 4]diazepine</t>
         </is>
       </c>
       <c r="D62"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>클래리트로마이신(Clarithromycin)</t>
-        </is>
-      </c>
-      <c r="F62"/>
+          <t>클로자핀(Clozapine)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ICH Q3A/Q3B에 따라 관리</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>비변이원성 불순물, SAR/read-across, 참조물질 N-nitroso-N-desmethyl-azithromycin</t>
-        </is>
-      </c>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H62"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>N-nitroso-aryl piperazine / N-nitroso-desalkylquetiapine, NDAQ</t>
+          <t>N-nitroso-N-desmethyl clarithromycin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11-(4-Nitrosopiperazin-1-yl)dibenzo[b,f][1,4]thiazepine</t>
+          <t>N-[(2S,3R,4S,6R)-2-[[(3R,4S,5S,6R,7R,9R,11R,12R,13S,14R)-14-ethyl-12,13-dihydroxy-4-[(2R,4R,5S,6S)-5-hydroxy-4-methoxy-4,6-dimethyloxan-2-yl]oxy-7-methoxy-3,5,7,9,11,13-hexamethyl-2,10-dioxo-oxacyclotetradec-6-yl]oxy]-3-hydroxy-6-methyloxan-4-yl]-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D63"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>쿠에티아핀(Quetiapine)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>클래리트로마이신(Clarithromycin)</t>
+        </is>
+      </c>
+      <c r="F63"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H63"/>
+          <t>ICH Q3A/Q3B에 따라 관리</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>비변이원성 불순물, SAR/read-across, 참조물질 N-nitroso-N-desmethyl-azithromycin</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>N-nitroso Quetiapine HEEP Impurity</t>
+          <t>N-nitroso-aryl piperazine / N-nitroso-desalkylquetiapine, NDAQ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2-(2-(4-nitrosopiperazin-1-yl)ethoxy)ethan-1-ol</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>73486-81-4</t>
-        </is>
-      </c>
+          <t>11-(4-Nitrosopiperazin-1-yl)dibenzo[b,f][1,4]thiazepine</t>
+        </is>
+      </c>
+      <c r="D64"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>쿠에티아핀(Quetiapine)</t>
         </is>
       </c>
-      <c r="F64"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>AMES 음성</t>
-        </is>
-      </c>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H64"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>N-nitroso-ketamine</t>
+          <t>N-nitroso Quetiapine HEEP Impurity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>N-[1-(2-chlorophenyl)-2-oxocyclohexyl]-N-methylnitrous amide</t>
+          <t>2-(2-(4-nitrosopiperazin-1-yl)ethoxy)ethan-1-ol</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>86144-35-6</t>
+          <t>73486-81-4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>케타민(Ketamine)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>쿠에티아핀(Quetiapine)</t>
+        </is>
+      </c>
+      <c r="F65"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="H65"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>AMES 음성</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>N-nitroso-caspofungin</t>
+          <t>N-nitroso-ketamine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>(10R,12S)-N-((2R,9S,11R,12S,14aS,15S,20S,25aS)-20-((R)-3-amino-1-hydroxypropyl)-12-((2-aminoethyl)(nitroso)amino)-23-((1S,2S)-1,2-dihydroxy-2-(4-hydroxyphenyl)ethyl)-2,11,15-trihydroxy-6-((R)-1-hydroxyethyl)-5,8,14,19,22,25-hexaoxotetracosahydro-1H-dipyrrolo[2,1-c:2`,1`-l][1,4,7,10,13,16]hexaazacyclohenicosin-9-yl)-10,12-dimethyltetradecanamide</t>
-        </is>
-      </c>
-      <c r="D66"/>
+          <t>N-[1-(2-chlorophenyl)-2-oxocyclohexyl]-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>86144-35-6</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>카스포펀진(Caspofungin)</t>
+          <t>케타민(Ketamine)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2685,39 +2685,35 @@
       <c r="H66"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Indapamide Impurity A</t>
+          <t>N-nitroso-caspofungin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2-methyl-1-nitroso-2,3-dihydroindole</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>85440-79-5</t>
-        </is>
-      </c>
+          <t>(10R,12S)-N-((2R,9S,11R,12S,14aS,15S,20S,25aS)-20-((R)-3-amino-1-hydroxypropyl)-12-((2-aminoethyl)(nitroso)amino)-23-((1S,2S)-1,2-dihydroxy-2-(4-hydroxyphenyl)ethyl)-2,11,15-trihydroxy-6-((R)-1-hydroxyethyl)-5,8,14,19,22,25-hexaoxotetracosahydro-1H-dipyrrolo[2,1-c:2`,1`-l][1,4,7,10,13,16]hexaazacyclohenicosin-9-yl)-10,12-dimethyltetradecanamide</t>
+        </is>
+      </c>
+      <c r="D67"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>인다파미드(Indapamide)</t>
+          <t>카스포펀진(Caspofungin)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2728,39 +2724,39 @@
       <c r="H67"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">N-nitroso-iminodiacetic acid </t>
+          <t>Indapamide Impurity A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2-[carboxymethyl(nitroso)amino] acetic acid</t>
+          <t>2-methyl-1-nitroso-2,3-dihydroindole</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25081-31-6</t>
+          <t>85440-79-5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>이소소르비드 모노니트레이트(Isosorbide mononitrate)</t>
+          <t>인다파미드(Indapamide)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2778,22 +2774,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">N-nitroso-ethylenediamine-triacetic acid </t>
+          <t xml:space="preserve">N-nitroso-iminodiacetic acid </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2-[carboxymethyl-[2-[carboxymethyl(nitroso)amino] ethyl]amino]acetic acid</t>
+          <t>2-[carboxymethyl(nitroso)amino] acetic acid</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>862542-34-5</t>
+          <t>25081-31-6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2821,28 +2817,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>N-nitroso-imatinib</t>
+          <t xml:space="preserve">N-nitroso-ethylenediamine-triacetic acid </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>N-(4-methyl-3-(nitroso(4-(pyridin-3-yl)pyrimidin-2-yl)amino)phenyl)-4-((4-methylpiperazin-1-yl)methyl)benzamide</t>
-        </is>
-      </c>
-      <c r="D70"/>
+          <t>2-[carboxymethyl-[2-[carboxymethyl(nitroso)amino] ethyl]amino]acetic acid</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>862542-34-5</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>이매티닙(Imatinib)</t>
+          <t>이소소르비드 모노니트레이트(Isosorbide mononitrate)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2860,76 +2860,72 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethylorphenadrine, NMOA</t>
+          <t>N-nitroso-imatinib</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>N-Methyl-N-(2-(phenyl(o-tolyl)methoxy)ethyl)nitrous Amide</t>
+          <t>N-(4-methyl-3-(nitroso(4-(pyridin-3-yl)pyrimidin-2-yl)amino)phenyl)-4-((4-methylpiperazin-1-yl)methyl)benzamide</t>
         </is>
       </c>
       <c r="D71"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>오르페나드린(Orphenadrine)</t>
+          <t>이매티닙(Imatinib)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H71"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>N-nitroso-folic acid, NFA</t>
+          <t>N-nitroso-N-desmethylorphenadrine, NMOA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2-[[4-[(2-amino-4-oxo-3H-pteridin-6-yl)methyl-nitrosoamino] benzoyl]amino]pentanedioic acid</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>26360-21-4</t>
-        </is>
-      </c>
+          <t>N-Methyl-N-(2-(phenyl(o-tolyl)methoxy)ethyl)nitrous Amide</t>
+        </is>
+      </c>
+      <c r="D72"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>엽산/폴산(Folic acid)</t>
+          <t>오르페나드린(Orphenadrine)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H72"/>
@@ -2942,395 +2938,399 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>N-nitroso-epinephrine</t>
+          <t>N-nitroso-folic acid, NFA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>N-[(2R)-2-(3,4-dihydroxyphenyl)-2-hydroxyethyl]-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D73"/>
+          <t>2-[[4-[(2-amino-4-oxo-3H-pteridin-6-yl)methyl-nitrosoamino] benzoyl]amino]pentanedioic acid</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>26360-21-4</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>에피네프린(Epinephrine)</t>
+          <t>엽산/폴산(Folic acid)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H73"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>N-nitroso-esmolol</t>
+          <t>N-nitroso-epinephrine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Methyl 3-(4-(2-hydroxy-3-(isopropyl(nitroso)amino)propoxy)phenyl)propanoate</t>
+          <t>N-[(2R)-2-(3,4-dihydroxyphenyl)-2-hydroxyethyl]-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D74"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>에스몰롤(Esmolol)</t>
+          <t>에피네프린(Epinephrine)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H74"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2025-02-18</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-edoxaban</t>
+          <t>N-nitroso-esmolol</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">N-1-(5-chloropyridin-2-yl)-N2-((1S,2R,4S)-4-(dimethylcarbamoyl)-2-(5-nitroso-4,5,6,7-tetrahydrothiazolo[5,4-c]pyridine-2-carboxamido) cyclohexyl) oxalamide </t>
+          <t>Methyl 3-(4-(2-hydroxy-3-(isopropyl(nitroso)amino)propoxy)phenyl)propanoate</t>
         </is>
       </c>
       <c r="D75"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>에독사반(Edoxaban)</t>
+          <t>에스몰롤(Esmolol)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H75"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2024-01-18</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>N-nitroso-enalapril</t>
+          <t>N-nitroso-desmethyl-edoxaban</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(2S)-1-[(2S)-2-[[(2S)-1-ethoxy-1-oxo-4-phenylbutan-2-yl]-nitrosoamino]propanoyl]pyrrolidine-2-carboxylic acid</t>
+          <t xml:space="preserve">N-1-(5-chloropyridin-2-yl)-N2-((1S,2R,4S)-4-(dimethylcarbamoyl)-2-(5-nitroso-4,5,6,7-tetrahydrothiazolo[5,4-c]pyridine-2-carboxamido) cyclohexyl) oxalamide </t>
         </is>
       </c>
       <c r="D76"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>에날라프릴(Enalapril)</t>
+          <t>에독사반(Edoxaban)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H76"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-02-18</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>N-nitroso-ambroxol</t>
+          <t>N-nitroso-enalapril</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>N-[(2-amino-3,5-dibromophenyl)methyl]-N-[4-hydroxycyclohexyl]nitrous amide</t>
+          <t>(2S)-1-[(2S)-2-[[(2S)-1-ethoxy-1-oxo-4-phenylbutan-2-yl]-nitrosoamino]propanoyl]pyrrolidine-2-carboxylic acid</t>
         </is>
       </c>
       <c r="D77"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>암브록솔(Ambroxol)</t>
-        </is>
-      </c>
-      <c r="F77"/>
+          <t>에날라프릴(Enalapril)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>AMES 음성</t>
-        </is>
-      </c>
+      <c r="H77"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3-amino-N-nitrosopiperidine</t>
+          <t>N-nitroso-ambroxol</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1-nitrosopiperidin-3-amine</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2819242-71-0</t>
-        </is>
-      </c>
+          <t>N-[(2-amino-3,5-dibromophenyl)methyl]-N-[4-hydroxycyclohexyl]nitrous amide</t>
+        </is>
+      </c>
+      <c r="D78"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>알로글립틴(Alogliptin)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>암브록솔(Ambroxol)</t>
+        </is>
+      </c>
+      <c r="F78"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H78"/>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>AMES 음성</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>N-nitroso-apixaban impurity B</t>
+          <t>3-amino-N-nitrosopiperidine</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>5-[4-[3-carbamoyl-1-(4-methoxyphenyl)-7-oxo-4,5-dihydropyrazolo[3,4-c]pyridin-6-yl]-N-nitrosoanilino]pentanoic acid</t>
-        </is>
-      </c>
-      <c r="D79"/>
+          <t>1-nitrosopiperidin-3-amine</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2819242-71-0</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>아픽사반(Apixaban)</t>
+          <t>알로글립틴(Alogliptin)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H79"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-01-18</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>N-nitroso-atomoxetine</t>
+          <t>N-nitroso-apixaban impurity B</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>N-methyl-N-[(3R)-3-(2-methylphenoxy)-3-phenylpropyl]nitrous amide</t>
+          <t>5-[4-[3-carbamoyl-1-(4-methoxyphenyl)-7-oxo-4,5-dihydropyrazolo[3,4-c]pyridin-6-yl]-N-nitrosoanilino]pentanoic acid</t>
         </is>
       </c>
       <c r="D80"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>아토목세틴(Atomoxetine)</t>
-        </is>
-      </c>
-      <c r="F80"/>
+          <t>아픽사반(Apixaban)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>SAR/read-across, 참조물질 NNK</t>
-        </is>
-      </c>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H80"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>N-nitroso-atenolol</t>
+          <t>N-nitroso-atomoxetine</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2-[4-[2-hydroxy-3-[nitroso(propan-2-yl)amino]propoxy]phenyl]acetamide</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>134720-04-0</t>
-        </is>
-      </c>
+          <t>N-methyl-N-[(3R)-3-(2-methylphenoxy)-3-phenylpropyl]nitrous amide</t>
+        </is>
+      </c>
+      <c r="D81"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>아테놀롤(Atenolol)</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>아토목세틴(Atomoxetine)</t>
+        </is>
+      </c>
+      <c r="F81"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H81"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SAR/read-across, 참조물질 NNK</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-azithromycin</t>
+          <t>N-nitroso-atenolol</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>(2R,3S,4R,5R,8R,10R,11R,12S,13S,14R)-2-ethyl-3,4,10-trihydroxy-13-[(2R,4R,5S,6S)-5-hydroxy-4-methoxy-4,6-dimethyloxan-2-yl]oxy-11-[(2S,3R,4S,6R)-3-hydroxy-6-methyl-4-(methylamino)oxan-2-yl]oxy-3,5,6,8,10,12,14-heptamethyl-1-oxa-6-azacyclopentadecan-15-one</t>
-        </is>
-      </c>
-      <c r="D82"/>
+          <t>2-[4-[2-hydroxy-3-[nitroso(propan-2-yl)amino]propoxy]phenyl]acetamide</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>134720-04-0</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>아지스로마이신(Azithromycin)</t>
-        </is>
-      </c>
-      <c r="F82"/>
+          <t>아테놀롤(Atenolol)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ICH Q3A/Q3B에 따라 관리</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>비변이원성 불순물, in vivo</t>
-        </is>
-      </c>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H82"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2023-12-13</t>
@@ -3340,17 +3340,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>N-nitroso-azaerythromycin</t>
+          <t>N-nitroso-N-desmethyl-azithromycin</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>(2R, 3S, 4R, 5R, 8R, 10R, 11R, 12S, 13S, 14R)-11-(((2S, 3R, 4S, 6R)-4-(dimethylamino)-3-hydroxy-6-methyltetrahydro-2H-pyran-2-yl)oxy)-2-ethyl-3, 4, 10-trihydroxy-13-(((2R, 4R, 5S, 6S)-5-hydroxy-4-methoxy-4, 6-dimethyltetrahydro-2H-pyran-2-yl)oxy)-3, 5, 8, 10, 12, 14-hexamethyl-6-nitroso-1-oxa-6-azacyclopentadecan-15-one</t>
+          <t>(2R,3S,4R,5R,8R,10R,11R,12S,13S,14R)-2-ethyl-3,4,10-trihydroxy-13-[(2R,4R,5S,6S)-5-hydroxy-4-methoxy-4,6-dimethyloxan-2-yl]oxy-11-[(2S,3R,4S,6R)-3-hydroxy-6-methyl-4-(methylamino)oxan-2-yl]oxy-3,5,6,8,10,12,14-heptamethyl-1-oxa-6-azacyclopentadecan-15-one</t>
         </is>
       </c>
       <c r="D83"/>
@@ -3379,76 +3379,72 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-azelastine</t>
+          <t>N-nitroso-azaerythromycin</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4-(4-Chlorobenzyl)-2-(1-nitrosoazepan-4-yl)phthalazin-1(2H)-one</t>
+          <t>(2R, 3S, 4R, 5R, 8R, 10R, 11R, 12S, 13S, 14R)-11-(((2S, 3R, 4S, 6R)-4-(dimethylamino)-3-hydroxy-6-methyltetrahydro-2H-pyran-2-yl)oxy)-2-ethyl-3, 4, 10-trihydroxy-13-(((2R, 4R, 5S, 6S)-5-hydroxy-4-methoxy-4, 6-dimethyltetrahydro-2H-pyran-2-yl)oxy)-3, 5, 8, 10, 12, 14-hexamethyl-6-nitroso-1-oxa-6-azacyclopentadecan-15-one</t>
         </is>
       </c>
       <c r="D84"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>아젤라스틴(Azelastine)</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>아지스로마이신(Azithromycin)</t>
+        </is>
+      </c>
+      <c r="F84"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H84"/>
+          <t>ICH Q3A/Q3B에 따라 관리</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>비변이원성 불순물, in vivo</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1-(2,3-dichlorophenyl)-4-nitrosopiperazine</t>
+          <t>N-nitroso-desmethyl-azelastine</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1-(2,3-dichlorophenyl)-4-nitrosopiperazine</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2221987-86-4</t>
-        </is>
-      </c>
+          <t>4-(4-Chlorobenzyl)-2-(1-nitrosoazepan-4-yl)phthalazin-1(2H)-one</t>
+        </is>
+      </c>
+      <c r="D85"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>아리피프라졸(Aripiprazole)</t>
+          <t>아젤라스틴(Azelastine)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H85"/>
@@ -3461,71 +3457,71 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>N-nitroso-silodosin</t>
+          <t>1-(2,3-dichlorophenyl)-4-nitrosopiperazine</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1-(3-hydroxypropyl)-5-[(2R)-2-[nitroso-[2-[2-(2,2,2-trifluoroethoxy)phenoxy]ethyl]amino]propyl]-2,3-dihydroindole-7-carboxamide</t>
-        </is>
-      </c>
-      <c r="D86"/>
+          <t>1-(2,3-dichlorophenyl)-4-nitrosopiperazine</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2221987-86-4</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>실로도신(Silodosin)</t>
+          <t>아리피프라졸(Aripiprazole)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H86"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>N-nitroso-cilazapril</t>
+          <t>N-nitroso-silodosin</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>(1S, 9S)-9-[[(1S)-1-(Ethoxycarbonyl)-3-phenylpropyl]nitrosoamino]octahydro-10-oxo-6H-pyridazino[1, 2-a][1, 2]diazepine-1-carboxylic Acid</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>1053740-92-3</t>
-        </is>
-      </c>
+          <t>1-(3-hydroxypropyl)-5-[(2R)-2-[nitroso-[2-[2-(2,2,2-trifluoroethoxy)phenoxy]ethyl]amino]propyl]-2,3-dihydroindole-7-carboxamide</t>
+        </is>
+      </c>
+      <c r="D87"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>실라자프릴(Cilazapril)</t>
+          <t>실로도신(Silodosin)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3536,73 +3532,73 @@
       <c r="H87"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-02-18</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-sildenafil</t>
+          <t>N-nitroso-cilazapril</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>5-(2-ethoxy-5-((4-nitrosopiperazin-1-yl)sulfonyl)phenyl)-1-methyl-3-propyl-1H-pyrazolo[4, 3-d]pyrimidin-7(6H)-one</t>
-        </is>
-      </c>
-      <c r="D88"/>
+          <t>(1S, 9S)-9-[[(1S)-1-(Ethoxycarbonyl)-3-phenylpropyl]nitrosoamino]octahydro-10-oxo-6H-pyridazino[1, 2-a][1, 2]diazepine-1-carboxylic Acid</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1053740-92-3</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>실데나필(Sildenafil)</t>
+          <t>실라자프릴(Cilazapril)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H88"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1-diphenylmethyl-4-nitrosopiperazine</t>
+          <t>N-nitroso-N-desmethyl-sildenafil</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1-benzhydryl-4-nitrosopiperazine</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>1698-25-5</t>
-        </is>
-      </c>
+          <t>5-(2-ethoxy-5-((4-nitrosopiperazin-1-yl)sulfonyl)phenyl)-1-methyl-3-propyl-1H-pyrazolo[4, 3-d]pyrimidin-7(6H)-one</t>
+        </is>
+      </c>
+      <c r="D89"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>신나리진(cinnarizine)</t>
+          <t>실데나필(Sildenafil)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3618,290 +3614,294 @@
       <c r="H89"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>N-nitroso-ciprofloxacin</t>
+          <t>1-diphenylmethyl-4-nitrosopiperazine</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1-cyclopropyl-6-fluoro-7-(4-nitrosopiperazin-1-yl)-4-oxoquinoline-3-carboxylic acid</t>
+          <t>1-benzhydryl-4-nitrosopiperazine</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>864443-44-7</t>
+          <t>1698-25-5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>시프로플록사신(Ciprofloxacin)</t>
-        </is>
-      </c>
-      <c r="F90"/>
+          <t>신나리진(cinnarizine)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ICH Q3A/Q3B에 따라 관리</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>비변이원성 불순물, in vivo</t>
-        </is>
-      </c>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H90"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-01-09</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-citalopram</t>
+          <t>N-nitroso-ciprofloxacin</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>N-(3-(5-cyano-1-(4-fluorophenyl)-1, 3-dihydroisobenzofuran-1-yl)propyl)-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D91"/>
+          <t>1-cyclopropyl-6-fluoro-7-(4-nitrosopiperazin-1-yl)-4-oxoquinoline-3-carboxylic acid</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>864443-44-7</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>시탈로프람(Citalopram)</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>시프로플록사신(Ciprofloxacin)</t>
+        </is>
+      </c>
+      <c r="F91"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="H91"/>
+          <t>ICH Q3A/Q3B에 따라 관리</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>비변이원성 불순물, in vivo</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7-nitroso-3-(trifluoromethyl)-5,6,7,8-tetrahydro[1,2,4]triazolo-[4,3-a]pyrazine (NTTP)</t>
+          <t>N-nitroso-N-desmethyl-citalopram</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>7-nitroso-3-(trifluoromethyl)-6,8-dihydro-5H-[1,2,4]triazolo[4,3-a]pyrazine</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2892260-32-9</t>
-        </is>
-      </c>
+          <t>N-(3-(5-cyano-1-(4-fluorophenyl)-1, 3-dihydroisobenzofuran-1-yl)propyl)-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D92"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>시타글립틴(Sitagliptin)</t>
+          <t>시탈로프람(Citalopram)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H92"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2,2,5-trimethyl-3-nitroso-1,3-oxazolidine</t>
+          <t>7-nitroso-3-(trifluoromethyl)-5,6,7,8-tetrahydro[1,2,4]triazolo-[4,3-a]pyrazine (NTTP)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2,2,5-trimethyl-3-nitroso-1,3-oxazolidine</t>
+          <t>7-nitroso-3-(trifluoromethyl)-6,8-dihydro-5H-[1,2,4]triazolo[4,3-a]pyrazine</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>77400-46-5</t>
+          <t>2892260-32-9</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>시아노코발라민(Cyanocobalamine)</t>
+          <t>시타글립틴(Sitagliptin)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H93"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-10-25</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>N-nitroso-cinacalcet</t>
+          <t>2,2,5-trimethyl-3-nitroso-1,3-oxazolidine</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>(R)-N-(1-(naphthalen-1-yl)ethyl)-N-(3-(3-(trifluoromethyl)phenyl)propyl)nitrous amide</t>
-        </is>
-      </c>
-      <c r="D94"/>
+          <t>2,2,5-trimethyl-3-nitroso-1,3-oxazolidine</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>77400-46-5</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>시나칼세트(Cinacalcet)</t>
+          <t>시아노코발라민(Cyanocobalamine)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H94"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>N-nitroso-pseudoephedrine</t>
+          <t>N-nitroso-cinacalcet</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>N-((1S,2S)-1-Hydroxy-1-phenylpropan-2-yl)-N-methylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1850-88-0</t>
-        </is>
-      </c>
+          <t>(R)-N-(1-(naphthalen-1-yl)ethyl)-N-(3-(3-(trifluoromethyl)phenyl)propyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D95"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>슈도에페드린(Pseudoephedrine)</t>
+          <t>시나칼세트(Cinacalcet)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H95"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-01-18</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-sumatriptan</t>
+          <t>N-nitroso-pseudoephedrine</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>N-methyl-1-(3-(2-(methyl(nitroso)amino)ethyl)-1H-indol-5-yl)methanesulfonamide</t>
-        </is>
-      </c>
-      <c r="D96"/>
+          <t>N-((1S,2S)-1-Hydroxy-1-phenylpropan-2-yl)-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1850-88-0</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>수마프립탄(Sumatriptan)</t>
+          <t>슈도에페드린(Pseudoephedrine)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H96"/>
@@ -3914,37 +3914,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>N-nitroso-sotalol</t>
+          <t>N-nitroso-N-desmethyl-sumatriptan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>N-[4-[1-hydroxy-2-[nitroso(propan-2-yl)amino]ethyl]phenyl]methanesulfonamide</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>134720-07-3</t>
-        </is>
-      </c>
+          <t>N-methyl-1-(3-(2-(methyl(nitroso)amino)ethyl)-1H-indol-5-yl)methanesulfonamide</t>
+        </is>
+      </c>
+      <c r="D97"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>소타롤(Sotalol)</t>
+          <t>수마프립탄(Sumatriptan)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H97"/>
@@ -3957,28 +3953,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>N-nitroso-celiprolol</t>
+          <t>N-nitroso-sotalol</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3-(3-Acetyl-4-(3-(tert-butyl(nitroso)amino)-2-hydroxypropoxy)phenyl)-1,1-diethylurea</t>
-        </is>
-      </c>
-      <c r="D98"/>
+          <t>N-[4-[1-hydroxy-2-[nitroso(propan-2-yl)amino]ethyl]phenyl]methanesulfonamide</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>134720-07-3</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>셀리프롤롤(Celiprolol)</t>
+          <t>소타롤(Sotalol)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3989,108 +3989,108 @@
       <c r="H98"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>N-nitroso-sertraline</t>
+          <t>N-nitroso-celiprolol</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>N-(4-(3, 4-dichlorophenyl)-1, 2, 3, 4-tetrahydronaphthalen-1-yl)-N-methylnitrous amide</t>
+          <t>3-(3-Acetyl-4-(3-(tert-butyl(nitroso)amino)-2-hydroxypropoxy)phenyl)-1,1-diethylurea</t>
         </is>
       </c>
       <c r="D99"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>설트랄린(Sertraline)</t>
+          <t>셀리프롤롤(Celiprolol)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H99"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>N-nitroso-salbutamol</t>
+          <t>N-nitroso-sertraline</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>N-tert-butyl-N-[2-hydroxy-2-[4-hydroxy-3-(hydroxymethyl)phenyl]ethyl]nitrous amide</t>
+          <t>N-(4-(3, 4-dichlorophenyl)-1, 2, 3, 4-tetrahydronaphthalen-1-yl)-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D100"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>살부타몰(Salbutamol)</t>
+          <t>설트랄린(Sertraline)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H100"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-02-18</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>N-nitroso-vildagliptin</t>
+          <t>N-nitroso-salbutamol</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>N-(2-((S)-2-cyanopyrrolidin-1-yl)-2-oxoethyl)-N-((1r,3R,5R,7S)-3-hydroxyadamantan-1-yl)nitrous amide</t>
+          <t>N-tert-butyl-N-[2-hydroxy-2-[4-hydroxy-3-(hydroxymethyl)phenyl]ethyl]nitrous amide</t>
         </is>
       </c>
       <c r="D101"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>빌다글립틴(Vildagliptin)</t>
+          <t>살부타몰(Salbutamol)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>N-nitroso vildagliptin amide impurity</t>
+          <t>N-nitroso-vildagliptin</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>(S)-1-(2-(((1r, 3R, 5R, 7S)-3-hydroxyadamantan-1-yl)(nitroso)amino)acetyl)pyrrolidine-2-carboxamide(S)-1-(2-(((1r, 3R, 5R, 7S)-3-hydroxyadamantan-1-yl)(nitroso)amino)acetyl)pyrrolidine-2-carboxamide</t>
+          <t>N-(2-((S)-2-cyanopyrrolidin-1-yl)-2-oxoethyl)-N-((1r,3R,5R,7S)-3-hydroxyadamantan-1-yl)nitrous amide</t>
         </is>
       </c>
       <c r="D102"/>
@@ -4145,39 +4145,35 @@
       <c r="H102"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>N-nitroso-bisoprolol (NBP)</t>
+          <t>N-nitroso vildagliptin amide impurity</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>N-[2-hydroxy-3-[4-(2-propan-2-yloxyethoxymethyl)phenoxy]propyl]-N-propan-2-ylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2820170-76-9</t>
-        </is>
-      </c>
+          <t>(S)-1-(2-(((1r, 3R, 5R, 7S)-3-hydroxyadamantan-1-yl)(nitroso)amino)acetyl)pyrrolidine-2-carboxamide(S)-1-(2-(((1r, 3R, 5R, 7S)-3-hydroxyadamantan-1-yl)(nitroso)amino)acetyl)pyrrolidine-2-carboxamide</t>
+        </is>
+      </c>
+      <c r="D103"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>비소프롤롤(Bisoprolol)</t>
+          <t>빌다글립틴(Vildagliptin)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4188,39 +4184,39 @@
       <c r="H103"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>N-nitroso-bupropion</t>
+          <t>N-nitroso-bisoprolol (NBP)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>N-tert-butyl-N-[1-(3-chlorophenyl)-1-oxopropan-2-yl]nitrous amide</t>
+          <t>N-[2-hydroxy-3-[4-(2-propan-2-yloxyethoxymethyl)phenoxy]propyl]-N-propan-2-ylnitrous amide</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2763780-10-3</t>
+          <t>2820170-76-9</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>부프로피온(Bupropion)</t>
+          <t>비소프롤롤(Bisoprolol)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4238,66 +4234,70 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>N-nitroso-buspirone Impurity 1</t>
+          <t>N-nitroso-bupropion</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2-(4-nitrosopiperazine-1-yl)-pyrimidine</t>
+          <t>N-tert-butyl-N-[1-(3-chlorophenyl)-1-oxopropan-2-yl]nitrous amide</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>872826-80-7</t>
+          <t>2763780-10-3</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>부스피론(Buspirone)</t>
+          <t>부프로피온(Bupropion)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H105"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>N-nitroso-vortioxetine</t>
+          <t>N-nitroso-buspirone Impurity 1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1-[2-(2,4-dimethylphenyl)sulfanylphenyl]-4-nitrosopiperazine</t>
-        </is>
-      </c>
-      <c r="D106"/>
+          <t>2-(4-nitrosopiperazine-1-yl)-pyrimidine</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>872826-80-7</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>보티옥세틴(Vortioxetine)</t>
+          <t>부스피론(Buspirone)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4313,34 +4313,30 @@
       <c r="H106"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-02-18</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3-(dimethylamino)propyl 2-[benzyl(nitroso)amino]benzoate</t>
+          <t>N-nitroso-vortioxetine</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3-(dimethylamino)propyl 2-[benzyl(nitroso)amino]benzoate</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>87453-76-7</t>
-        </is>
-      </c>
+          <t>1-[2-(2,4-dimethylphenyl)sulfanylphenyl]-4-nitrosopiperazine</t>
+        </is>
+      </c>
+      <c r="D107"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>벤지다민(Benzydamine)</t>
+          <t>보티옥세틴(Vortioxetine)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4356,184 +4352,188 @@
       <c r="H107"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>N-nitroso-betaxolol</t>
+          <t>3-(dimethylamino)propyl 2-[benzyl(nitroso)amino]benzoate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>N-(3-(4-(2-(cyclopropylmethoxy)ethyl)phenoxy)-2-hydroxypropyl)-N-isopropylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D108"/>
+          <t>3-(dimethylamino)propyl 2-[benzyl(nitroso)amino]benzoate</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>87453-76-7</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>베탁솔롤(Betaxolol)</t>
+          <t>벤지다민(Benzydamine)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H108"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2025-02-18</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>N-nitroso-betahistine</t>
+          <t>N-nitroso-betaxolol</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>N-methyl-N-(2-pyridin-2-ylethyl)nitrous amide</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>32635-81-7</t>
-        </is>
-      </c>
+          <t>N-(3-(4-(2-(cyclopropylmethoxy)ethyl)phenoxy)-2-hydroxypropyl)-N-isopropylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D109"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>베타히스틴(Betahisitne)</t>
+          <t>베탁솔롤(Betaxolol)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H109"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>N-nitroso-valsartan cyano-desvalerylmethylester</t>
+          <t>N-nitroso-betahistine</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>(S)-Methyl 2-(((2'-cyano-[1,1'-biphenyl]-4-yl)methyl)(nitroso)amino)-3-methylbutanoate</t>
-        </is>
-      </c>
-      <c r="D110"/>
+          <t>N-methyl-N-(2-pyridin-2-ylethyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>32635-81-7</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>발사르탄(Valsartan)</t>
+          <t>베타히스틴(Betahisitne)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H110"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>N-nitroso-N-methyl-valacyclovir</t>
+          <t>N-nitroso-valsartan cyano-desvalerylmethylester</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2-[(2-amino-6-oxo-1H-purin-9-yl)methoxy]ethyl 3-methyl-2-[methyl(nitroso)amino]butanoate</t>
+          <t>(S)-Methyl 2-(((2'-cyano-[1,1'-biphenyl]-4-yl)methyl)(nitroso)amino)-3-methylbutanoate</t>
         </is>
       </c>
       <c r="D111"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>발라시클로비르(Valacyclovir)</t>
+          <t>발사르탄(Valsartan)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H111"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>N-nitroso-N-ethyl-valacyclovir</t>
+          <t>N-nitroso-N-methyl-valacyclovir</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2-[(2-amino-6-oxo-1H-purin-9-yl)methoxy]ethyl 2-[ethyl(nitroso)amino]-3-methylbutanoate</t>
+          <t>2-[(2-amino-6-oxo-1H-purin-9-yl)methoxy]ethyl 3-methyl-2-[methyl(nitroso)amino]butanoate</t>
         </is>
       </c>
       <c r="D112"/>
@@ -4562,27 +4562,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>N-nitroso-varenicline, NNV</t>
+          <t>N-nitroso-N-ethyl-valacyclovir</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>(1R,12S)-14-nitroso-5,8,14-triazatetracyclo[10.3.1.02,11.04,9]hexadeca-2,4,6,8,10-pentaene</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2755871-02-2 </t>
-        </is>
-      </c>
+          <t>2-[(2-amino-6-oxo-1H-purin-9-yl)methoxy]ethyl 2-[ethyl(nitroso)amino]-3-methylbutanoate</t>
+        </is>
+      </c>
+      <c r="D113"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>바레니클린(Varenicline)</t>
+          <t>발라시클로비르(Valacyclovir)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4598,30 +4594,34 @@
       <c r="H113"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-mirtazepine</t>
+          <t>N-nitroso-varenicline, NNV</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2-nitroso-1, 2, 3, 4, 10, 14b-hexahydrobenzo[c]pyrazino[1, 2-a]pyrido[3, 2-f]azepine</t>
-        </is>
-      </c>
-      <c r="D114"/>
+          <t>(1R,12S)-14-nitroso-5,8,14-triazatetracyclo[10.3.1.02,11.04,9]hexadeca-2,4,6,8,10-pentaene</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2755871-02-2 </t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>미르타자핀(Mirtazapine)</t>
+          <t>바레니클린(Varenicline)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4637,30 +4637,30 @@
       <c r="H114"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>N-nitroso-mirabegron</t>
+          <t>N-nitroso-N-desmethyl-mirtazepine</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>(R)-2-(2-Aminothiazol-4-yl)-N-(4-(2-((2-hydroxy-2-phenylethyl)(nitroso)amino)ethyl)phenyl)acetamide</t>
+          <t>2-nitroso-1, 2, 3, 4, 10, 14b-hexahydrobenzo[c]pyrazino[1, 2-a]pyrido[3, 2-f]azepine</t>
         </is>
       </c>
       <c r="D115"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>미라베그론(Mirabegron)</t>
+          <t>미르타자핀(Mirtazapine)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4676,24 +4676,24 @@
       <c r="H115"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>N-(4-aminophenethyl)-N-(2-hydroxy-2-phenylethyl)nitrous amide</t>
+          <t>N-nitroso-mirabegron</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>(R)-N-(4-aminophenethyl)-N-(2-hydroxy-2-phenylethyl)nitrous amide</t>
+          <t>(R)-2-(2-Aminothiazol-4-yl)-N-(4-(2-((2-hydroxy-2-phenylethyl)(nitroso)amino)ethyl)phenyl)acetamide</t>
         </is>
       </c>
       <c r="D116"/>
@@ -4715,24 +4715,24 @@
       <c r="H116"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>N-(2-hydroxy-2-phenylethyl)-N-(4-nitrophenethyl)nitrous amide</t>
+          <t>N-(4-aminophenethyl)-N-(2-hydroxy-2-phenylethyl)nitrous amide</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>(R)-N-(2-hydroxy-2-phenylethyl)-N-(4-nitrophenethyl)nitrous amide</t>
+          <t>(R)-N-(4-aminophenethyl)-N-(2-hydroxy-2-phenylethyl)nitrous amide</t>
         </is>
       </c>
       <c r="D117"/>
@@ -4761,56 +4761,56 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>N-nitroso-moxifloxacin</t>
+          <t>N-(2-hydroxy-2-phenylethyl)-N-(4-nitrophenethyl)nitrous amide</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1-cyclopropyl-6-fluoro-8-methoxy-7-((4aS,7aS)-1-nitrosooctahydro-6H-pyrrolo[3,4-b]pyridin-6-yl)-4-oxo-1,4-dihydroquinoline-3-carboxylic acid</t>
+          <t>(R)-N-(2-hydroxy-2-phenylethyl)-N-(4-nitrophenethyl)nitrous amide</t>
         </is>
       </c>
       <c r="D118"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>목시플록사신(Moxifloxacin)</t>
+          <t>미라베그론(Mirabegron)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H118"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-02-18</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1-nitroso-pyrrolopiperidine</t>
+          <t>N-nitroso-moxifloxacin</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>(4aS,7aS)-1-Nitrosooctahydro-1H-pyrrolo[3,4-b]pyridine</t>
+          <t>1-cyclopropyl-6-fluoro-8-methoxy-7-((4aS,7aS)-1-nitrosooctahydro-6H-pyrrolo[3,4-b]pyridin-6-yl)-4-oxo-1,4-dihydroquinoline-3-carboxylic acid</t>
         </is>
       </c>
       <c r="D119"/>
@@ -4832,116 +4832,112 @@
       <c r="H119"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>N-nitroso-methylphenidate (NMPH)</t>
+          <t>1-nitroso-pyrrolopiperidine</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>methyl 2-(1-nitrosopiperidin-2-yl)-2-phenylacetate</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>55557-03-4</t>
-        </is>
-      </c>
+          <t>(4aS,7aS)-1-Nitrosooctahydro-1H-pyrrolo[3,4-b]pyridine</t>
+        </is>
+      </c>
+      <c r="D120"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>메틸페니데이트(Methylphenidate)</t>
-        </is>
-      </c>
-      <c r="F120"/>
+          <t>목시플록사신(Moxifloxacin)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>SAR/read-across, 참조물질 NPIP</t>
-        </is>
-      </c>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H120"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>N-nitroso-ritalinic acid</t>
+          <t>N-nitroso-methylphenidate (NMPH)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2-(1-nitrosopiperidin-2-yl)-2-phenylacetic acid</t>
-        </is>
-      </c>
-      <c r="D121"/>
+          <t>methyl 2-(1-nitrosopiperidin-2-yl)-2-phenylacetate</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>55557-03-4</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>메틸페니데이트(Methylphenidate)</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="F121"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H121"/>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>SAR/read-across, 참조물질 NPIP</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>N-nitroso-metoprolol</t>
+          <t>N-nitroso-ritalinic acid</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>N-[2-hydroxy-3-[4-(2-methoxyethyl)phenoxy]propyl]-N-propan-2-ylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>134720-05-1</t>
-        </is>
-      </c>
+          <t>2-(1-nitrosopiperidin-2-yl)-2-phenylacetic acid</t>
+        </is>
+      </c>
+      <c r="D122"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>메토프롤롤(Metoprolol)</t>
+          <t>메틸페니데이트(Methylphenidate)</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4957,30 +4953,34 @@
       <c r="H122"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>N-nitroso-meropenem</t>
+          <t>N-nitroso-metoprolol</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>(4R, 5S, 6S)-3-(((3S, 5S)-5-(dimethylcarbamoyl)-1-nitrosopyrrolidin-3-yl)thio)-6-((R)-1-hydroxyethyl)-4-methyl-7-oxo-1-azabicyclo[3.2.0]hept-2-ene-2-carboxylic acid</t>
-        </is>
-      </c>
-      <c r="D123"/>
+          <t>N-[2-hydroxy-3-[4-(2-methoxyethyl)phenoxy]propyl]-N-propan-2-ylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>134720-05-1</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>메로페넴(Meropenem)</t>
+          <t>메토프롤롤(Metoprolol)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5003,72 +5003,72 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>N-nitroso-2,4-thiazole amine (NNTA)</t>
+          <t>N-nitroso-meropenem</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>N-((2-isopropylthiazol-4-yl)methyl)-N-methylnitrous amide</t>
+          <t>(4R, 5S, 6S)-3-(((3S, 5S)-5-(dimethylcarbamoyl)-1-nitrosopyrrolidin-3-yl)thio)-6-((R)-1-hydroxyethyl)-4-methyl-7-oxo-1-azabicyclo[3.2.0]hept-2-ene-2-carboxylic acid</t>
         </is>
       </c>
       <c r="D124"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>리토나비르(Ritonavir), 코비시스타트(Cobicistat)</t>
+          <t>메로페넴(Meropenem)</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H124"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">N-nitroso-desformyl-riociguat </t>
+          <t>N-nitroso-2,4-thiazole amine (NNTA)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">N-(4,6-diamino-2-(1-(2-fluorobenzyl)-1H-pyrazolo[3,4-b]pyridin-3-yl)pyrimidin-5-yl)-N-methylnitrous </t>
+          <t>N-((2-isopropylthiazol-4-yl)methyl)-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D125"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>리오시구앗(Riociguat)</t>
+          <t>리토나비르(Ritonavir), 코비시스타트(Cobicistat)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H125"/>
@@ -5081,173 +5081,173 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>N-nitroso-lisinopril</t>
+          <t xml:space="preserve">N-nitroso-desformyl-riociguat </t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>N2-((S)-1-carboxy-3-phenylpropyl)-N2-nitroso-L-lysyl-L-proline</t>
+          <t xml:space="preserve">N-(4,6-diamino-2-(1-(2-fluorobenzyl)-1H-pyrazolo[3,4-b]pyridin-3-yl)pyrimidin-5-yl)-N-methylnitrous </t>
         </is>
       </c>
       <c r="D126"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>리시노프릴(Linsinopril)</t>
+          <t>리오시구앗(Riociguat)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H126"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>N-nitroso-ribociclib impurity 1</t>
+          <t>N-nitroso-lisinopril</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>7-cyclopentyl-N,N-dimethyl-2-((5-(4-nitrosopiperazin-1-yl)pyridine-2-yl)amino)-7H-pyrrolo[2,3-d]pyrimidine-6-carboxamide</t>
+          <t>N2-((S)-1-carboxy-3-phenylpropyl)-N2-nitroso-L-lysyl-L-proline</t>
         </is>
       </c>
       <c r="D127"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>리보시클립(Ribociclib)</t>
+          <t>리시노프릴(Linsinopril)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H127"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl rivastigmine</t>
+          <t>N-nitroso-ribociclib impurity 1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>[3-[(1S)-1-[methyl(nitroso)amino] ethyl]phenyl] N-ethyl-N-methyl carbamate</t>
+          <t>7-cyclopentyl-N,N-dimethyl-2-((5-(4-nitrosopiperazin-1-yl)pyridine-2-yl)amino)-7H-pyrrolo[2,3-d]pyrimidine-6-carboxamide</t>
         </is>
       </c>
       <c r="D128"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>리바스티그민(Rivastigmine)</t>
+          <t>리보시클립(Ribociclib)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H128"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Rivaroxaban nitroso Impurity 5</t>
+          <t>N-nitroso-N-desmethyl rivastigmine</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>N-(3-Chloro-2-hydroxypropyl)-N-(4-(3-oxomorpholino)phenyl)nitrous amide</t>
+          <t>[3-[(1S)-1-[methyl(nitroso)amino] ethyl]phenyl] N-ethyl-N-methyl carbamate</t>
         </is>
       </c>
       <c r="D129"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>리바록사반(Rivaroxaban)</t>
+          <t>리바스티그민(Rivastigmine)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H129"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Rivaroxaban nitroso Impurity 2</t>
+          <t>Rivaroxaban nitroso Impurity 5</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>N-(3-(1,3-dioxoisoindolin-2-yl)-2-hydroxypropyl)-N-(4-(3-oxomorpholino) phenyl)nitrous amide</t>
+          <t>N-(3-Chloro-2-hydroxypropyl)-N-(4-(3-oxomorpholino)phenyl)nitrous amide</t>
         </is>
       </c>
       <c r="D130"/>
@@ -5276,24 +5276,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Rivaroxaban nitroso Impurity 1</t>
+          <t>Rivaroxaban nitroso Impurity 2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>N-(2-hydroxyethyl)-N-phenyl-nitrous amide</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>25413-76-7</t>
-        </is>
-      </c>
+          <t>N-(3-(1,3-dioxoisoindolin-2-yl)-2-hydroxypropyl)-N-(4-(3-oxomorpholino) phenyl)nitrous amide</t>
+        </is>
+      </c>
+      <c r="D131"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>리바록사반(Rivaroxaban)</t>
@@ -5319,20 +5315,24 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>N-Nitroso-rivaroxaban open-ring acid</t>
+          <t>Rivaroxaban nitroso Impurity 1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>(S)-2-(2-((4-(5-((5-chlorothiophene-2-carboxamido)methyl)-2-oxooxazolidin-3-yl)phenyl)(nitroso)amino)ethoxy) acetic acid</t>
-        </is>
-      </c>
-      <c r="D132"/>
+          <t>N-(2-hydroxyethyl)-N-phenyl-nitrous amide</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>25413-76-7</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>리바록사반(Rivaroxaban)</t>
@@ -5351,24 +5351,24 @@
       <c r="H132"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>N-Nitroso-rivaroxaban amide</t>
+          <t>N-Nitroso-rivaroxaban open-ring acid</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>(S)-5-chloro-N-(2-hydroxy-3-(nitroso (4-(3-oxomorpholino)phenyl)amino) propyl)thiophene-2-carboxamide</t>
+          <t>(S)-2-(2-((4-(5-((5-chlorothiophene-2-carboxamido)methyl)-2-oxooxazolidin-3-yl)phenyl)(nitroso)amino)ethoxy) acetic acid</t>
         </is>
       </c>
       <c r="D133"/>
@@ -5397,33 +5397,33 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>N-nitroso-desethyllidocaine</t>
+          <t>N-Nitroso-rivaroxaban amide</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>N-(2,6-dimethylphenyl)-2-[ethyl(nitroso)amino]acetamide</t>
+          <t>(S)-5-chloro-N-(2-hydroxy-3-(nitroso (4-(3-oxomorpholino)phenyl)amino) propyl)thiophene-2-carboxamide</t>
         </is>
       </c>
       <c r="D134"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>리도카인(Lidocaine)</t>
+          <t>리바록사반(Rivaroxaban)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H134"/>
@@ -5436,62 +5436,62 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>N-nitroso-folinic acid</t>
+          <t>N-nitroso-desethyllidocaine</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>N-[4-[[(2-amino-5-formyl-1,4,5,6,7,8-hexahydro-4-oxo-6-pteridinyl)methyl](nitroso)amino]benzoyl]-L-glutamic acid</t>
+          <t>N-(2,6-dimethylphenyl)-2-[ethyl(nitroso)amino]acetamide</t>
         </is>
       </c>
       <c r="D135"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>류코보린(Leucovorin)</t>
+          <t>리도카인(Lidocaine)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H135"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>N-nitroso-2,6-pipecoloxilidide</t>
+          <t>N-nitroso-folinic acid</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>N-(2,6-dimethylphenyl)-1-nitrosopiperidine-2-carboxamide</t>
+          <t>N-[4-[[(2-amino-5-formyl-1,4,5,6,7,8-hexahydro-4-oxo-6-pteridinyl)methyl](nitroso)amino]benzoyl]-L-glutamic acid</t>
         </is>
       </c>
       <c r="D136"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>로피바카인(Ropivacaine)</t>
+          <t>류코보린(Leucovorin)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5514,27 +5514,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-levofloxacin</t>
+          <t>N-nitroso-2,6-pipecoloxilidide</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>(2S)-7-fluoro-2-methyl-6-(4-nitrosopiperazin-1-yl)-10-oxo-4-oxa-1-azatricyclo[7.3.1.05,13]trideca-5(13),6,8,11-tetraene-11-carboxylic acid</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>1152314-62-9</t>
-        </is>
-      </c>
+          <t>N-(2,6-dimethylphenyl)-1-nitrosopiperidine-2-carboxamide</t>
+        </is>
+      </c>
+      <c r="D137"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>레보플록사신(Levofloxacin)</t>
+          <t>로피바카인(Ropivacaine)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5557,37 +5553,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>N-nitroso-rasagiline</t>
+          <t>N-nitroso-N-desmethyl-levofloxacin</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>N-[(1R)-2,3-dihydro-1H-inden-1-yl]-N-prop-2-ynylnitrous amide</t>
+          <t>(2S)-7-fluoro-2-methyl-6-(4-nitrosopiperazin-1-yl)-10-oxo-4-oxa-1-azatricyclo[7.3.1.05,13]trideca-5(13),6,8,11-tetraene-11-carboxylic acid</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2470278-90-9</t>
+          <t>1152314-62-9</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>라사길린(Rasagiline)</t>
+          <t>레보플록사신(Levofloxacin)</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H138"/>
@@ -5600,37 +5596,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>N-nitroso-labetalol</t>
+          <t>N-nitroso-rasagiline</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2-hydroxy-5-[1-hydroxy-2-[nitroso(4-phenylbutan-2-yl)amino]ethyl]benzamide</t>
+          <t>N-[(1R)-2,3-dihydro-1H-inden-1-yl]-N-prop-2-ynylnitrous amide</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2820170-74-7</t>
+          <t>2470278-90-9</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>라베타롤(Labetalol)</t>
+          <t>라사길린(Rasagiline)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H139"/>
@@ -5643,28 +5639,32 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>N-nitroso-ramipril</t>
+          <t>N-nitroso-labetalol</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>(2S,3aS,6aS)-1-(N-((S)-1-ethoxy-1-oxo-4-phenylbutan-2-yl)-N-nitroso-L-alanyl)octahydrocyclopenta[b]pyrrole-2-carboxylic acid</t>
-        </is>
-      </c>
-      <c r="D140"/>
+          <t>2-hydroxy-5-[1-hydroxy-2-[nitroso(4-phenylbutan-2-yl)amino]ethyl]benzamide</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2820170-74-7</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>라미프릴(Ramipril)</t>
+          <t>라베타롤(Labetalol)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5682,200 +5682,200 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>N-nitroso-ranolazine impurity 1</t>
+          <t>N-nitroso-ramipril</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1-(2-methoxyphenoxy)-3-(4-nitrosopiperazin-1-yl)propan-2-ol</t>
+          <t>(2S,3aS,6aS)-1-(N-((S)-1-ethoxy-1-oxo-4-phenylbutan-2-yl)-N-nitroso-L-alanyl)octahydrocyclopenta[b]pyrrole-2-carboxylic acid</t>
         </is>
       </c>
       <c r="D141"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>라놀라진(Ranolazine)</t>
+          <t>라미프릴(Ramipril)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H141"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>N-nitroso-diclofenac</t>
+          <t>N-nitroso-ranolazine impurity 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2-[2-(2,6-dichloro-N-nitrosoanilino)phenyl]acetic acid</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>66505-80-4</t>
-        </is>
-      </c>
+          <t>1-(2-methoxyphenoxy)-3-(4-nitrosopiperazin-1-yl)propan-2-ol</t>
+        </is>
+      </c>
+      <c r="D142"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>디클로페낙(Diclofenac)</t>
+          <t>라놀라진(Ranolazine)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H142"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-diphenhydramine</t>
+          <t>N-nitroso-diclofenac</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>N-(2-benzhydryloxyethyl)-N-methylnitrous amide</t>
+          <t>2-[2-(2,6-dichloro-N-nitrosoanilino)phenyl]acetic acid</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>55855-43-1</t>
+          <t>66505-80-4</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>디멘히드리네이트(Dimenhydrinate), 디펜히드라민(Diphenhydramine)</t>
+          <t>디클로페낙(Diclofenac)</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H143"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>N-nitroso-duloxetine</t>
+          <t>N-nitroso-N-desmethyl-diphenhydramine</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>(S)-N-methyl-N-(3-(naphthalen-1-yloxy)-3-(thiophen-2-yl)propyl)nitrous amide</t>
-        </is>
-      </c>
-      <c r="D144"/>
+          <t>N-(2-benzhydryloxyethyl)-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>55855-43-1</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>둘록세틴(Duloxetine)</t>
-        </is>
-      </c>
-      <c r="F144"/>
+          <t>디멘히드리네이트(Dimenhydrinate), 디펜히드라민(Diphenhydramine)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>SAR/read-across, 참조물질 NNK</t>
-        </is>
-      </c>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="H144"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-01-09</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>N-nitroso-N-methyl-2-[1-phenyl-1-(2-pyridinyl)methoxy]ethanamine</t>
+          <t>N-nitroso-duloxetine</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>N-methyl-N-(2-(phenyl(pyridin-2-yl)methoxy)ethyl)nitrous amide</t>
+          <t>(S)-N-methyl-N-(3-(naphthalen-1-yloxy)-3-(thiophen-2-yl)propyl)nitrous amide</t>
         </is>
       </c>
       <c r="D145"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>독실아민(Doxylamine)</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>둘록세틴(Duloxetine)</t>
+        </is>
+      </c>
+      <c r="F145"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="H145"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>SAR/read-across, 참조물질 NNK</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr">
         <is>
           <t>2023-12-13</t>
@@ -5885,33 +5885,33 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-doxycycline</t>
+          <t>N-nitroso-N-methyl-2-[1-phenyl-1-(2-pyridinyl)methoxy]ethanamine</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>(4S,4aR,5S,5aR,6R,12aR)-1,5,10,11,12a-pentahydroxy-6-methyl-4-[methyl(nitroso)amino]-3,12-dioxo-4a,5,5a,6-tetrahydro-4H-tetracene-2-carboxamide</t>
+          <t>N-methyl-N-(2-(phenyl(pyridin-2-yl)methoxy)ethyl)nitrous amide</t>
         </is>
       </c>
       <c r="D146"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>독시사이클린(Doxycycline)</t>
+          <t>독실아민(Doxylamine)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H146"/>
@@ -5924,33 +5924,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>N-nitroso-nordoxepin</t>
+          <t>N-nitroso-N-desmethyl-doxycycline</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>N-[(3E or 3Z)-3-(6H-benzo[c][1]benzoxepin-11-ylidene)propyl]-N-methylnitrous amide</t>
+          <t>(4S,4aR,5S,5aR,6R,12aR)-1,5,10,11,12a-pentahydroxy-6-methyl-4-[methyl(nitroso)amino]-3,12-dioxo-4a,5,5a,6-tetrahydro-4H-tetracene-2-carboxamide</t>
         </is>
       </c>
       <c r="D147"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>독세핀(Doxepin)</t>
+          <t>독시사이클린(Doxycycline)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H147"/>
@@ -5963,33 +5963,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>N-nitroso-dorzolamide</t>
+          <t>N-nitroso-nordoxepin</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>(4S, 6S)-4-(ethyl(nitroso)amino)-6-methyl-5, 6-dihydro-4H-thieno[2, 3-b]thiopyran-2-sulfonamide 7, 7-dioxide</t>
+          <t>N-[(3E or 3Z)-3-(6H-benzo[c][1]benzoxepin-11-ylidene)propyl]-N-methylnitrous amide</t>
         </is>
       </c>
       <c r="D148"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>도르졸라미드(Dorzolamide)</t>
+          <t>독세핀(Doxepin)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H148"/>
@@ -6002,115 +6002,111 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-dextromethorphan</t>
+          <t>N-nitroso-dorzolamide</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>(4bS,8aS,9S)-3-methoxy-11-nitroso-6,7,8,8a,9,10-hexahydro-5H-9,4b-(epiminoethano)phenanthrene</t>
+          <t>(4S, 6S)-4-(ethyl(nitroso)amino)-6-methyl-5, 6-dihydro-4H-thieno[2, 3-b]thiopyran-2-sulfonamide 7, 7-dioxide</t>
         </is>
       </c>
       <c r="D149"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>덱스트로메토르판(Dextromethorphan)</t>
+          <t>도르졸라미드(Dorzolamide)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H149"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-desvenlafaxine</t>
+          <t>N-nitroso-N-desmethyl-dextromethorphan</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>N-(2-(1-Hydroxycyclohexyl)-2-(4-hydroxyphenyl)ethyl)-N-methylnitrous amide</t>
+          <t>(4bS,8aS,9S)-3-methoxy-11-nitroso-6,7,8,8a,9,10-hexahydro-5H-9,4b-(epiminoethano)phenanthrene</t>
         </is>
       </c>
       <c r="D150"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>데스벤라팍신(Desvenlafaxine)</t>
+          <t>덱스트로메토르판(Dextromethorphan)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H150"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>N-nitroso-desloratadine</t>
+          <t>N-nitroso-N-desmethyl-desvenlafaxine</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>13-chloro-2-(1-nitrosopiperidin-4-ylidene)-4-azatricyclo [9.4.0.03,8]pentadeca-1(11),3(8),4,6,12,14-hexaene</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>1246819-22-6</t>
-        </is>
-      </c>
+          <t>N-(2-(1-Hydroxycyclohexyl)-2-(4-hydroxyphenyl)ethyl)-N-methylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D151"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>데스로라타딘(Desloratadine)</t>
+          <t>데스벤라팍신(Desvenlafaxine)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H151"/>
@@ -6123,204 +6119,204 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>N-nitroso-dabigatran etexilate</t>
+          <t>N-nitroso-desloratadine</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ethyl3-(2-(((4-(N-((hexyloxy)carbonyl)carbamimidoyl)phenyl)(nitroso)amino)methyl)-1-methyl-N-(pyridin-2-yl)-1H-benzo[d]imidazole-5-carboxamido)propanoate</t>
-        </is>
-      </c>
-      <c r="D152"/>
+          <t>13-chloro-2-(1-nitrosopiperidin-4-ylidene)-4-azatricyclo [9.4.0.03,8]pentadeca-1(11),3(8),4,6,12,14-hexaene</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>1246819-22-6</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>다비가트란(Dabigatran)</t>
-        </is>
-      </c>
-      <c r="F152"/>
+          <t>데스로라타딘(Desloratadine)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>AMES 음성</t>
-        </is>
-      </c>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H152"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>N-nitroso-N-desmethyl-nintedanib</t>
+          <t>N-nitroso-dabigatran etexilate</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Methyl (Z)-3-(((4-(N-methyl-2-(4-nitrosopiperazin-1-yl)acetamido)phenyl)amino)(phenyl)methylene)-2-oxoindoline-6-carboxylate</t>
+          <t>Ethyl3-(2-(((4-(N-((hexyloxy)carbonyl)carbamimidoyl)phenyl)(nitroso)amino)methyl)-1-methyl-N-(pyridin-2-yl)-1H-benzo[d]imidazole-5-carboxamido)propanoate</t>
         </is>
       </c>
       <c r="D153"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>닌테다닙(Nintedanib)</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>다비가트란(Dabigatran)</t>
+        </is>
+      </c>
+      <c r="F153"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H153"/>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>AMES 음성</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>N-nitroso-nortriptyline (NNORT)</t>
+          <t>N-nitroso-N-desmethyl-nintedanib</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>N-methyl-N-[3-(2-tricyclo[9.4.0.0^3,8] pentadeca-1(15),3,5,7,11,13-hexaenylidene)propyl]nitrous amide</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>55855-42-0</t>
-        </is>
-      </c>
+          <t>Methyl (Z)-3-(((4-(N-methyl-2-(4-nitrosopiperazin-1-yl)acetamido)phenyl)amino)(phenyl)methylene)-2-oxoindoline-6-carboxylate</t>
+        </is>
+      </c>
+      <c r="D154"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>노르트립틸린(Nortriptyline), 아미트립틸린(Amitriptyline)</t>
+          <t>닌테다닙(Nintedanib)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H154"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-03-20</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>N-nitroso-nebivolol (NNEB)</t>
+          <t>N-nitroso-nortriptyline (NNORT)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>N,N-bis[2-(6-fluoro-3,4-dihydro-2H-chromen-2-yl)-2-hydroxyethyl]nitrous amide</t>
+          <t>N-methyl-N-[3-(2-tricyclo[9.4.0.0^3,8] pentadeca-1(15),3,5,7,11,13-hexaenylidene)propyl]nitrous amide</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1391051-68-5</t>
+          <t>55855-42-0</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>네비보롤(Nebivolol)</t>
+          <t>노르트립틸린(Nortriptyline), 아미트립틸린(Amitriptyline)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H155"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-11-06</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2-nitroso-octahydrocyclopenta(c)pyrrole</t>
+          <t>N-nitroso-nebivolol (NNEB)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2-nitroso-3,3a,4,5,6,6a-hexahydro-1H-cyclopenta[c]pyrrole</t>
+          <t>N,N-bis[2-(6-fluoro-3,4-dihydro-2H-chromen-2-yl)-2-hydroxyethyl]nitrous amide</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>54786-86-6</t>
+          <t>1391051-68-5</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>글리클라지드(Gliclazide)</t>
-        </is>
-      </c>
-      <c r="F156"/>
+          <t>네비보롤(Nebivolol)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>SAR/read-across, 참조물질 NPYR</t>
-        </is>
-      </c>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="H156"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>2023-12-13</t>
@@ -6330,104 +6326,104 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>N-nitroso-desmethyl-galantamine</t>
+          <t>2-nitroso-octahydrocyclopenta(c)pyrrole</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>(4aS,6R,8aS)-3-methoxy-11-nitroso-4a,5,9,10,11,12-hexahydro-6H-benzo[2,3]benzofuro[4,3-cd]azepin-6-ol</t>
-        </is>
-      </c>
-      <c r="D157"/>
+          <t>2-nitroso-3,3a,4,5,6,6a-hexahydro-1H-cyclopenta[c]pyrrole</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>54786-86-6</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>갈란타민(Galantamine)</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>글리클라지드(Gliclazide)</t>
+        </is>
+      </c>
+      <c r="F157"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="H157"/>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>SAR/read-across, 참조물질 NPYR</t>
+        </is>
+      </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>N-nitroso-N-methylaniline (NMPA)</t>
+          <t>N-nitroso-desmethyl-galantamine</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>N-methyl-N-phenylnitrous amide</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>614-00-6</t>
-        </is>
-      </c>
+          <t>(4aS,6R,8aS)-3-methoxy-11-nitroso-4a,5,9,10,11,12-hexahydro-6H-benzo[2,3]benzofuro[4,3-cd]azepin-6-ol</t>
+        </is>
+      </c>
+      <c r="D158"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>갈란타민(Galantamine)</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H158"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-06-12</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1-methyl-4-nitrosopiperazine (MeNP)</t>
+          <t>N-nitroso-N-methylaniline (NMPA)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>1-methyl-4-nitrosopiperazine</t>
+          <t>N-methyl-N-phenylnitrous amide</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>16339-07-4</t>
+          <t>614-00-6</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6437,40 +6433,40 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H159"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-02-18</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>N-nitroso-N-methyl-4-aminobutyric acid (NMBA)</t>
+          <t>1-methyl-4-nitrosopiperazine (MeNP)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>4-[methyl(nitroso)amino]butanoic acid</t>
+          <t>1-methyl-4-nitrosopiperazine</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>61445-55-4</t>
+          <t>16339-07-4</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6480,40 +6476,40 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H160"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-01-09</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>N-nitroso-ethylisopropylamine (NEIPA)</t>
+          <t>N-nitroso-N-methyl-4-aminobutyric acid (NMBA)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>N-ethyl-N-propan-2-ylnitrous amide</t>
+          <t>4-[methyl(nitroso)amino]butanoic acid</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>16339-04-1</t>
+          <t>61445-55-4</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6523,12 +6519,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H161"/>
@@ -6541,22 +6537,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>N-nitroso-diisopropylamine (NDIPA)</t>
+          <t>N-nitroso-ethylisopropylamine (NEIPA)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>N,N-di(propan-2-yl)nitrous amide</t>
+          <t>N-ethyl-N-propan-2-ylnitrous amide</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>601-77-4</t>
+          <t>16339-04-1</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6566,12 +6562,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H162"/>
@@ -6584,22 +6580,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>N-nitroso-pyrrolidine (NPYR)</t>
+          <t>N-nitroso-diisopropylamine (NDIPA)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>1-nitrosopyrrolidine</t>
+          <t>N,N-di(propan-2-yl)nitrous amide</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>930-55-2</t>
+          <t>601-77-4</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6607,38 +6603,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F163"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="H163"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2024-12-04</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>N-nitroso-piperidine (NPIP)</t>
+          <t>N-nitroso-pyrrolidine (NPYR)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>1-nitrosopiperidine</t>
+          <t>1-nitrosopyrrolidine</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>100-75-4</t>
+          <t>930-55-2</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6649,7 +6649,7 @@
       <c r="F164"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="H164"/>
@@ -6662,22 +6662,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>N-nitroso-morpholine (NMOR)</t>
+          <t>N-nitroso-piperidine (NPIP)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>4-nitrosomorpholine</t>
+          <t>1-nitrosopiperidine</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>59-89-2</t>
+          <t>100-75-4</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6688,35 +6688,35 @@
       <c r="F165"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H165"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2022-02-17</t>
+          <t>2023-12-13</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>N-nitroso-dipropylamine (NDPA)</t>
+          <t>N-nitroso-morpholine (NMOR)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>N,N-dipropylnitrous amide</t>
+          <t>4-nitrosomorpholine</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>621-64-7</t>
+          <t>59-89-2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6727,39 +6727,35 @@
       <c r="F166"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>26.5</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>SAR/read-across, 참조물질 NDEA</t>
-        </is>
-      </c>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="H166"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2022-02-17</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>N-nitroso-di-n-butylamine (NDBA)</t>
+          <t>N-nitroso-dipropylamine (NDPA)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>N,N-dibutylnitrous amide</t>
+          <t>N,N-dipropylnitrous amide</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>924-16-3</t>
+          <t>621-64-7</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6780,29 +6776,29 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-18</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>N-nitroso-diethylamine (NDEA)</t>
+          <t>N-nitroso-di-n-butylamine (NDBA)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>N,N-diethylnitrous amide</t>
+          <t>N,N-dibutylnitrous amide</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>55-18-5</t>
+          <t>924-16-3</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6816,32 +6812,36 @@
           <t>26.5</t>
         </is>
       </c>
-      <c r="H168"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>SAR/read-across, 참조물질 NDEA</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2021-11-09</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>N-nitroso-dimethylamine (NDMA)</t>
+          <t>N-nitroso-diethylamine (NDEA)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>N,N-dimethylnitrous amide</t>
+          <t>N,N-diethylnitrous amide</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>62-75-9</t>
+          <t>55-18-5</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6852,11 +6852,50 @@
       <c r="F169"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="H169"/>
       <c r="I169" t="inlineStr">
+        <is>
+          <t>2018-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>N-nitroso-dimethylamine (NDMA)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>N,N-dimethylnitrous amide</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>62-75-9</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H170"/>
+      <c r="I170" t="inlineStr">
         <is>
           <t>2018-08-06</t>
         </is>
